--- a/Udemy Excel 101.xlsx
+++ b/Udemy Excel 101.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8ef12d157d92b731/Documents/GitHub/Robert-Rookie-project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8761CF19-0046-4715-B8FB-9230E793B6F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{8761CF19-0046-4715-B8FB-9230E793B6F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42A629D9-F71F-4FF3-B08D-322117EDA3A6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F602598-B120-46E6-997C-287E091787E5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
   <si>
     <t>Monthly Budget</t>
   </si>
@@ -61,47 +61,14 @@
   <si>
     <t>Total</t>
   </si>
-  <si>
-    <t>Jan</t>
-  </si>
-  <si>
-    <t>Feb</t>
-  </si>
-  <si>
-    <t>Mar</t>
-  </si>
-  <si>
-    <t>April</t>
-  </si>
-  <si>
-    <t>May</t>
-  </si>
-  <si>
-    <t>Jun</t>
-  </si>
-  <si>
-    <t>July</t>
-  </si>
-  <si>
-    <t>Aug</t>
-  </si>
-  <si>
-    <t>Sept</t>
-  </si>
-  <si>
-    <t>Oct</t>
-  </si>
-  <si>
-    <t>Nov</t>
-  </si>
-  <si>
-    <t>Dec</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="mmm\-yyyy"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -131,8 +98,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -471,6 +439,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" customWidth="1"/>
+    <col min="2" max="13" width="12.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -482,41 +451,41 @@
       <c r="A3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L3" t="s">
-        <v>18</v>
-      </c>
-      <c r="M3" t="s">
-        <v>19</v>
+      <c r="B3" s="1">
+        <v>45658</v>
+      </c>
+      <c r="C3" s="1">
+        <v>45689</v>
+      </c>
+      <c r="D3" s="1">
+        <v>45717</v>
+      </c>
+      <c r="E3" s="1">
+        <v>45748</v>
+      </c>
+      <c r="F3" s="1">
+        <v>45778</v>
+      </c>
+      <c r="G3" s="1">
+        <v>45809</v>
+      </c>
+      <c r="H3" s="1">
+        <v>45839</v>
+      </c>
+      <c r="I3" s="1">
+        <v>45870</v>
+      </c>
+      <c r="J3" s="1">
+        <v>45901</v>
+      </c>
+      <c r="K3" s="1">
+        <v>45931</v>
+      </c>
+      <c r="L3" s="1">
+        <v>45962</v>
+      </c>
+      <c r="M3" s="1">
+        <v>45992</v>
       </c>
       <c r="N3" t="s">
         <v>7</v>

--- a/Udemy Excel 101.xlsx
+++ b/Udemy Excel 101.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8ef12d157d92b731/Documents/GitHub/Robert-Rookie-project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{8761CF19-0046-4715-B8FB-9230E793B6F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42A629D9-F71F-4FF3-B08D-322117EDA3A6}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="8_{8761CF19-0046-4715-B8FB-9230E793B6F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7619FF0-F888-4BD8-91EF-61FB4C46FC94}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F602598-B120-46E6-997C-287E091787E5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
   <si>
     <t>Monthly Budget</t>
   </si>
@@ -60,22 +60,47 @@
   </si>
   <si>
     <t>Total</t>
+  </si>
+  <si>
+    <t>Percent</t>
+  </si>
+  <si>
+    <t>Item A</t>
+  </si>
+  <si>
+    <t>Item B</t>
+  </si>
+  <si>
+    <t>Item C</t>
+  </si>
+  <si>
+    <t>Sub Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tax </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="mmm\-yyyy"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="mmm\-yyyy"/>
+    <numFmt numFmtId="165" formatCode="_-[$€-2]\ * #,##0.00_-;\-[$€-2]\ * #,##0.00_-;_-[$€-2]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Verdana"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -98,9 +123,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -116,6 +144,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -435,19 +467,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2E5EBEE-2860-4ED5-9D0E-88B7E3B3261C}">
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" customWidth="1"/>
     <col min="2" max="13" width="12.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -490,8 +522,11 @@
       <c r="N3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -531,8 +566,16 @@
       <c r="M4">
         <v>725</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N4">
+        <f t="shared" ref="N4:N8" si="0">SUM(B4:M4)</f>
+        <v>8700</v>
+      </c>
+      <c r="O4">
+        <f>N4/$N$9</f>
+        <v>0.54875741137883183</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -572,8 +615,16 @@
       <c r="M5">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N5">
+        <f t="shared" si="0"/>
+        <v>240</v>
+      </c>
+      <c r="O5">
+        <f t="shared" ref="O5:O8" si="1">N5/$N$9</f>
+        <v>1.5138135486312602E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -613,8 +664,16 @@
       <c r="M6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N6">
+        <f t="shared" si="0"/>
+        <v>1600</v>
+      </c>
+      <c r="O6">
+        <f t="shared" si="1"/>
+        <v>0.10092090324208401</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -654,8 +713,16 @@
       <c r="M7">
         <v>450</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N7">
+        <f t="shared" si="0"/>
+        <v>4950</v>
+      </c>
+      <c r="O7">
+        <f t="shared" si="1"/>
+        <v>0.31222404440519741</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -695,9 +762,115 @@
       <c r="M8">
         <v>75</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N8">
+        <f t="shared" si="0"/>
+        <v>364</v>
+      </c>
+      <c r="O8">
+        <f t="shared" si="1"/>
+        <v>2.2959505487574115E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <f>SUM(B4:B8)</f>
+        <v>1560</v>
+      </c>
+      <c r="C9">
+        <f t="shared" ref="C9:M9" si="2">SUM(C4:C8)</f>
+        <v>1615</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="2"/>
+        <v>1560</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="2"/>
+        <v>1570</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="2"/>
+        <v>1230</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="2"/>
+        <v>1190</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="2"/>
+        <v>1220</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="2"/>
+        <v>1130</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="2"/>
+        <v>1170</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="2"/>
+        <v>1209</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="2"/>
+        <v>1130</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="2"/>
+        <v>1270</v>
+      </c>
+      <c r="N9">
+        <f>SUM(B9:M9)</f>
+        <v>15854</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="B14" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="B15" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="2">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="B16" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="B17" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="2">
+        <f>SUM(C14:C16)</f>
+        <v>305</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="B18" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" s="3">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="B19" s="4" t="s">
         <v>7</v>
       </c>
     </row>

--- a/Udemy Excel 101.xlsx
+++ b/Udemy Excel 101.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8ef12d157d92b731/Documents/GitHub/Robert-Rookie-project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="8_{8761CF19-0046-4715-B8FB-9230E793B6F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7619FF0-F888-4BD8-91EF-61FB4C46FC94}"/>
+  <xr:revisionPtr revIDLastSave="53" documentId="8_{8761CF19-0046-4715-B8FB-9230E793B6F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30FBC74C-ADE4-48C9-B663-D986E6BF1A00}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F602598-B120-46E6-997C-287E091787E5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
   <si>
     <t>Monthly Budget</t>
   </si>
@@ -78,6 +78,15 @@
   </si>
   <si>
     <t xml:space="preserve">Tax </t>
+  </si>
+  <si>
+    <t>MIN</t>
+  </si>
+  <si>
+    <t>MAX</t>
+  </si>
+  <si>
+    <t>AVERAGE</t>
   </si>
 </sst>
 </file>
@@ -88,7 +97,7 @@
     <numFmt numFmtId="164" formatCode="mmm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="_-[$€-2]\ * #,##0.00_-;\-[$€-2]\ * #,##0.00_-;_-[$€-2]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -101,6 +110,14 @@
       <color theme="1"/>
       <name val="Verdana"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -123,12 +140,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -467,7 +485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2E5EBEE-2860-4ED5-9D0E-88B7E3B3261C}">
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" customWidth="1"/>
@@ -572,7 +590,7 @@
       </c>
       <c r="O4">
         <f>N4/$N$9</f>
-        <v>0.54875741137883183</v>
+        <v>0.54446460980036293</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
@@ -621,7 +639,7 @@
       </c>
       <c r="O5">
         <f t="shared" ref="O5:O8" si="1">N5/$N$9</f>
-        <v>1.5138135486312602E-2</v>
+        <v>1.5019713373803117E-2</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
@@ -641,36 +659,36 @@
         <v>400</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="N6">
         <f t="shared" si="0"/>
-        <v>1600</v>
+        <v>1725</v>
       </c>
       <c r="O6">
         <f t="shared" si="1"/>
-        <v>0.10092090324208401</v>
+        <v>0.1079541898742099</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
@@ -719,7 +737,7 @@
       </c>
       <c r="O7">
         <f t="shared" si="1"/>
-        <v>0.31222404440519741</v>
+        <v>0.30978158833468927</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
@@ -768,7 +786,7 @@
       </c>
       <c r="O8">
         <f t="shared" si="1"/>
-        <v>2.2959505487574115E-2</v>
+        <v>2.2779898616934725E-2</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
@@ -793,85 +811,248 @@
       </c>
       <c r="F9">
         <f t="shared" si="2"/>
-        <v>1230</v>
+        <v>1240</v>
       </c>
       <c r="G9">
         <f t="shared" si="2"/>
-        <v>1190</v>
+        <v>1195</v>
       </c>
       <c r="H9">
         <f t="shared" si="2"/>
-        <v>1220</v>
+        <v>1237</v>
       </c>
       <c r="I9">
         <f t="shared" si="2"/>
-        <v>1130</v>
+        <v>1138</v>
       </c>
       <c r="J9">
         <f t="shared" si="2"/>
-        <v>1170</v>
+        <v>1180</v>
       </c>
       <c r="K9">
         <f t="shared" si="2"/>
-        <v>1209</v>
+        <v>1224</v>
       </c>
       <c r="L9">
         <f t="shared" si="2"/>
-        <v>1130</v>
+        <v>1155</v>
       </c>
       <c r="M9">
         <f t="shared" si="2"/>
-        <v>1270</v>
+        <v>1305</v>
       </c>
       <c r="N9">
         <f>SUM(B9:M9)</f>
-        <v>15854</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" ht="16.2" x14ac:dyDescent="0.3">
-      <c r="B14" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" ht="16.2" x14ac:dyDescent="0.3">
-      <c r="B15" s="4" t="s">
+        <v>15979</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11">
+        <f>MIN(B4:B8)</f>
+        <v>15</v>
+      </c>
+      <c r="C11">
+        <f t="shared" ref="C11:M11" si="3">MIN(C4:C8)</f>
+        <v>20</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="C15" s="2">
-        <v>150</v>
+      <c r="G11">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="M11">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12">
+        <f>MAX(B4:B8)</f>
+        <v>725</v>
+      </c>
+      <c r="C12">
+        <f t="shared" ref="C12:M12" si="4">MAX(C4:C8)</f>
+        <v>725</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="4"/>
+        <v>725</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="4"/>
+        <v>725</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="4"/>
+        <v>725</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="4"/>
+        <v>725</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="4"/>
+        <v>725</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="4"/>
+        <v>725</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="4"/>
+        <v>725</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="4"/>
+        <v>725</v>
+      </c>
+      <c r="L12">
+        <f t="shared" si="4"/>
+        <v>725</v>
+      </c>
+      <c r="M12">
+        <f t="shared" si="4"/>
+        <v>725</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13">
+        <f>AVERAGE(B4:B8)</f>
+        <v>312</v>
+      </c>
+      <c r="C13">
+        <f t="shared" ref="C13:M13" si="5">AVERAGE(C4:C8)</f>
+        <v>323</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="5"/>
+        <v>312</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="5"/>
+        <v>314</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="5"/>
+        <v>248</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="5"/>
+        <v>239</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="5"/>
+        <v>247.4</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="5"/>
+        <v>227.6</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="5"/>
+        <v>236</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="5"/>
+        <v>244.8</v>
+      </c>
+      <c r="L13">
+        <f t="shared" si="5"/>
+        <v>231</v>
+      </c>
+      <c r="M13">
+        <f t="shared" si="5"/>
+        <v>261</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="16.2" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" s="2">
-        <v>55</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="16.2" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" s="2">
-        <f>SUM(C14:C16)</f>
-        <v>305</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="16.2" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" s="3">
-        <v>0.08</v>
+        <v>11</v>
+      </c>
+      <c r="C18" s="2">
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="16.2" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="2">
+        <f>SUM(C16:C18)</f>
+        <v>305</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="B20" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="3">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="B21" s="4" t="s">
         <v>7</v>
+      </c>
+      <c r="C21" s="2">
+        <f>C19*(C20+1)</f>
+        <v>329.40000000000003</v>
       </c>
     </row>
   </sheetData>

--- a/Udemy Excel 101.xlsx
+++ b/Udemy Excel 101.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8ef12d157d92b731/Documents/GitHub/Robert-Rookie-project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8EF12D157D92B731/Documents/GitHub/Robert-Rookie-project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="53" documentId="8_{8761CF19-0046-4715-B8FB-9230E793B6F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30FBC74C-ADE4-48C9-B663-D986E6BF1A00}"/>
+  <xr:revisionPtr revIDLastSave="92" documentId="8_{8761CF19-0046-4715-B8FB-9230E793B6F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3A28C96-3F1C-4F57-9E56-9EBFDDF4DE28}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F602598-B120-46E6-997C-287E091787E5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
   <si>
     <t>Monthly Budget</t>
   </si>
@@ -87,6 +88,9 @@
   </si>
   <si>
     <t>AVERAGE</t>
+  </si>
+  <si>
+    <t>Counts</t>
   </si>
 </sst>
 </file>
@@ -162,10 +166,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -485,573 +485,626 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2E5EBEE-2860-4ED5-9D0E-88B7E3B3261C}">
-  <dimension ref="A1:O21"/>
+  <dimension ref="B3:P23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" customWidth="1"/>
     <col min="2" max="13" width="12.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="3" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="5" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="1">
+      <c r="C5" s="1">
         <v>45658</v>
       </c>
-      <c r="C3" s="1">
+      <c r="D5" s="1">
         <v>45689</v>
       </c>
-      <c r="D3" s="1">
+      <c r="E5" s="1">
         <v>45717</v>
       </c>
-      <c r="E3" s="1">
+      <c r="F5" s="1">
         <v>45748</v>
       </c>
-      <c r="F3" s="1">
+      <c r="G5" s="1">
         <v>45778</v>
       </c>
-      <c r="G3" s="1">
+      <c r="H5" s="1">
         <v>45809</v>
       </c>
-      <c r="H3" s="1">
+      <c r="I5" s="1">
         <v>45839</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J5" s="1">
         <v>45870</v>
       </c>
-      <c r="J3" s="1">
+      <c r="K5" s="1">
         <v>45901</v>
       </c>
-      <c r="K3" s="1">
+      <c r="L5" s="1">
         <v>45931</v>
       </c>
-      <c r="L3" s="1">
+      <c r="M5" s="1">
         <v>45962</v>
       </c>
-      <c r="M3" s="1">
+      <c r="N5" s="1">
         <v>45992</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O5" t="s">
         <v>7</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="6" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
         <v>2</v>
       </c>
-      <c r="B4">
-        <v>725</v>
-      </c>
-      <c r="C4">
-        <v>725</v>
-      </c>
-      <c r="D4">
-        <v>725</v>
-      </c>
-      <c r="E4">
-        <v>725</v>
-      </c>
-      <c r="F4">
-        <v>725</v>
-      </c>
-      <c r="G4">
-        <v>725</v>
-      </c>
-      <c r="H4">
-        <v>725</v>
-      </c>
-      <c r="I4">
-        <v>725</v>
-      </c>
-      <c r="J4">
-        <v>725</v>
-      </c>
-      <c r="K4">
-        <v>725</v>
-      </c>
-      <c r="L4">
-        <v>725</v>
-      </c>
-      <c r="M4">
-        <v>725</v>
-      </c>
-      <c r="N4">
-        <f t="shared" ref="N4:N8" si="0">SUM(B4:M4)</f>
+      <c r="C6">
+        <v>725</v>
+      </c>
+      <c r="D6">
+        <v>725</v>
+      </c>
+      <c r="E6">
+        <v>725</v>
+      </c>
+      <c r="F6">
+        <v>725</v>
+      </c>
+      <c r="G6">
+        <v>725</v>
+      </c>
+      <c r="H6">
+        <v>725</v>
+      </c>
+      <c r="I6">
+        <v>725</v>
+      </c>
+      <c r="J6">
+        <v>725</v>
+      </c>
+      <c r="K6">
+        <v>725</v>
+      </c>
+      <c r="L6">
+        <v>725</v>
+      </c>
+      <c r="M6">
+        <v>725</v>
+      </c>
+      <c r="N6">
+        <v>725</v>
+      </c>
+      <c r="O6">
+        <f>SUM(C6:N6)</f>
         <v>8700</v>
       </c>
-      <c r="O4">
-        <f>N4/$N$9</f>
+      <c r="P6">
+        <f>O6/$O$11</f>
         <v>0.54446460980036293</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="7" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
         <v>3</v>
       </c>
-      <c r="B5">
-        <v>20</v>
-      </c>
-      <c r="C5">
-        <v>20</v>
-      </c>
-      <c r="D5">
-        <v>20</v>
-      </c>
-      <c r="E5">
-        <v>20</v>
-      </c>
-      <c r="F5">
-        <v>20</v>
-      </c>
-      <c r="G5">
-        <v>20</v>
-      </c>
-      <c r="H5">
-        <v>20</v>
-      </c>
-      <c r="I5">
-        <v>20</v>
-      </c>
-      <c r="J5">
-        <v>20</v>
-      </c>
-      <c r="K5">
-        <v>20</v>
-      </c>
-      <c r="L5">
-        <v>20</v>
-      </c>
-      <c r="M5">
-        <v>20</v>
-      </c>
-      <c r="N5">
-        <f t="shared" si="0"/>
+      <c r="C7">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>20</v>
+      </c>
+      <c r="E7">
+        <v>20</v>
+      </c>
+      <c r="F7">
+        <v>20</v>
+      </c>
+      <c r="G7">
+        <v>20</v>
+      </c>
+      <c r="H7">
+        <v>20</v>
+      </c>
+      <c r="I7">
+        <v>20</v>
+      </c>
+      <c r="J7">
+        <v>20</v>
+      </c>
+      <c r="K7">
+        <v>20</v>
+      </c>
+      <c r="L7">
+        <v>20</v>
+      </c>
+      <c r="M7">
+        <v>20</v>
+      </c>
+      <c r="N7">
+        <v>20</v>
+      </c>
+      <c r="O7">
+        <f>SUM(C7:N7)</f>
         <v>240</v>
       </c>
-      <c r="O5">
-        <f t="shared" ref="O5:O8" si="1">N5/$N$9</f>
+      <c r="P7">
+        <f>O7/$O$11</f>
         <v>1.5019713373803117E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="8" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
         <v>4</v>
       </c>
-      <c r="B6">
+      <c r="C8">
         <v>400</v>
       </c>
-      <c r="C6">
+      <c r="D8">
         <v>400</v>
       </c>
-      <c r="D6">
+      <c r="E8">
         <v>400</v>
       </c>
-      <c r="E6">
+      <c r="F8">
         <v>400</v>
       </c>
-      <c r="F6">
+      <c r="G8">
         <v>10</v>
       </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-      <c r="H6">
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="I8">
         <v>17</v>
       </c>
-      <c r="I6">
+      <c r="J8">
         <v>8</v>
       </c>
-      <c r="J6">
+      <c r="K8">
         <v>10</v>
       </c>
-      <c r="K6">
+      <c r="L8">
         <v>15</v>
       </c>
-      <c r="L6">
+      <c r="M8">
         <v>25</v>
       </c>
-      <c r="M6">
+      <c r="N8">
         <v>35</v>
       </c>
-      <c r="N6">
-        <f t="shared" si="0"/>
+      <c r="O8">
+        <f>SUM(C8:N8)</f>
         <v>1725</v>
       </c>
-      <c r="O6">
-        <f t="shared" si="1"/>
+      <c r="P8">
+        <f>O8/$O$11</f>
         <v>0.1079541898742099</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9">
         <v>400</v>
       </c>
-      <c r="C7">
+      <c r="D9">
         <v>450</v>
       </c>
-      <c r="D7">
+      <c r="E9">
         <v>400</v>
       </c>
-      <c r="E7">
+      <c r="F9">
         <v>400</v>
       </c>
-      <c r="F7">
+      <c r="G9">
         <v>450</v>
       </c>
-      <c r="G7">
+      <c r="H9">
         <v>400</v>
       </c>
-      <c r="H7">
+      <c r="I9">
         <v>450</v>
       </c>
-      <c r="I7">
+      <c r="J9">
         <v>350</v>
       </c>
-      <c r="J7">
+      <c r="K9">
         <v>400</v>
       </c>
-      <c r="K7">
+      <c r="L9">
         <v>450</v>
       </c>
-      <c r="L7">
+      <c r="M9">
         <v>350</v>
       </c>
-      <c r="M7">
+      <c r="N9">
         <v>450</v>
       </c>
-      <c r="N7">
-        <f t="shared" si="0"/>
+      <c r="O9">
+        <f>SUM(C9:N9)</f>
         <v>4950</v>
       </c>
-      <c r="O7">
-        <f t="shared" si="1"/>
+      <c r="P9">
+        <f>O9/$O$11</f>
         <v>0.30978158833468927</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+    <row r="10" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
         <v>6</v>
       </c>
-      <c r="B8">
+      <c r="C10">
         <v>15</v>
       </c>
-      <c r="C8">
-        <v>20</v>
-      </c>
-      <c r="D8">
+      <c r="D10">
+        <v>20</v>
+      </c>
+      <c r="E10">
         <v>15</v>
       </c>
-      <c r="E8">
+      <c r="F10">
         <v>25</v>
       </c>
-      <c r="F8">
+      <c r="G10">
         <v>35</v>
       </c>
-      <c r="G8">
+      <c r="H10">
         <v>45</v>
       </c>
-      <c r="H8">
+      <c r="I10">
         <v>25</v>
       </c>
-      <c r="I8">
+      <c r="J10">
         <v>35</v>
       </c>
-      <c r="J8">
+      <c r="K10">
         <v>25</v>
       </c>
-      <c r="K8">
+      <c r="L10">
         <v>14</v>
       </c>
-      <c r="L8">
+      <c r="M10">
         <v>35</v>
       </c>
-      <c r="M8">
+      <c r="N10">
         <v>75</v>
       </c>
-      <c r="N8">
-        <f t="shared" si="0"/>
+      <c r="O10">
+        <f>SUM(C10:N10)</f>
         <v>364</v>
       </c>
-      <c r="O8">
-        <f t="shared" si="1"/>
+      <c r="P10">
+        <f>O10/$O$11</f>
         <v>2.2779898616934725E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+    <row r="11" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
         <v>7</v>
       </c>
-      <c r="B9">
-        <f>SUM(B4:B8)</f>
+      <c r="C11">
+        <f>SUM(C6:C10)</f>
         <v>1560</v>
       </c>
-      <c r="C9">
-        <f t="shared" ref="C9:M9" si="2">SUM(C4:C8)</f>
+      <c r="D11">
+        <f>SUM(D6:D10)</f>
         <v>1615</v>
       </c>
-      <c r="D9">
-        <f t="shared" si="2"/>
+      <c r="E11">
+        <f>SUM(E6:E10)</f>
         <v>1560</v>
       </c>
-      <c r="E9">
-        <f t="shared" si="2"/>
+      <c r="F11">
+        <f>SUM(F6:F10)</f>
         <v>1570</v>
       </c>
-      <c r="F9">
-        <f t="shared" si="2"/>
+      <c r="G11">
+        <f>SUM(G6:G10)</f>
         <v>1240</v>
       </c>
-      <c r="G9">
-        <f t="shared" si="2"/>
+      <c r="H11">
+        <f>SUM(H6:H10)</f>
         <v>1195</v>
       </c>
-      <c r="H9">
-        <f t="shared" si="2"/>
+      <c r="I11">
+        <f>SUM(I6:I10)</f>
         <v>1237</v>
       </c>
-      <c r="I9">
-        <f t="shared" si="2"/>
+      <c r="J11">
+        <f>SUM(J6:J10)</f>
         <v>1138</v>
       </c>
-      <c r="J9">
-        <f t="shared" si="2"/>
+      <c r="K11">
+        <f>SUM(K6:K10)</f>
         <v>1180</v>
       </c>
-      <c r="K9">
-        <f t="shared" si="2"/>
+      <c r="L11">
+        <f>SUM(L6:L10)</f>
         <v>1224</v>
       </c>
-      <c r="L9">
-        <f t="shared" si="2"/>
+      <c r="M11">
+        <f>SUM(M6:M10)</f>
         <v>1155</v>
       </c>
-      <c r="M9">
-        <f t="shared" si="2"/>
+      <c r="N11">
+        <f>SUM(N6:N10)</f>
         <v>1305</v>
       </c>
-      <c r="N9">
-        <f>SUM(B9:M9)</f>
+      <c r="O11">
+        <f>SUM(C11:N11)</f>
         <v>15979</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
+    <row r="13" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B13" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B11">
-        <f>MIN(B4:B8)</f>
+      <c r="C13">
+        <f>MIN(C6:C10)</f>
         <v>15</v>
       </c>
-      <c r="C11">
-        <f t="shared" ref="C11:M11" si="3">MIN(C4:C8)</f>
-        <v>20</v>
-      </c>
-      <c r="D11">
-        <f t="shared" si="3"/>
+      <c r="D13">
+        <f>MIN(D6:D10)</f>
+        <v>20</v>
+      </c>
+      <c r="E13">
+        <f>MIN(E6:E10)</f>
         <v>15</v>
       </c>
-      <c r="E11">
-        <f t="shared" si="3"/>
-        <v>20</v>
-      </c>
-      <c r="F11">
-        <f t="shared" si="3"/>
+      <c r="F13">
+        <f>MIN(F6:F10)</f>
+        <v>20</v>
+      </c>
+      <c r="G13">
+        <f>MIN(G6:G10)</f>
         <v>10</v>
       </c>
-      <c r="G11">
-        <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-      <c r="H11">
-        <f t="shared" si="3"/>
+      <c r="H13">
+        <f>MIN(H6:H10)</f>
+        <v>5</v>
+      </c>
+      <c r="I13">
+        <f>MIN(I6:I10)</f>
         <v>17</v>
       </c>
-      <c r="I11">
-        <f t="shared" si="3"/>
+      <c r="J13">
+        <f>MIN(J6:J10)</f>
         <v>8</v>
       </c>
-      <c r="J11">
-        <f t="shared" si="3"/>
+      <c r="K13">
+        <f>MIN(K6:K10)</f>
         <v>10</v>
       </c>
-      <c r="K11">
-        <f t="shared" si="3"/>
+      <c r="L13">
+        <f>MIN(L6:L10)</f>
         <v>14</v>
       </c>
-      <c r="L11">
-        <f t="shared" si="3"/>
-        <v>20</v>
-      </c>
-      <c r="M11">
-        <f t="shared" si="3"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
+      <c r="M13">
+        <f>MIN(M6:M10)</f>
+        <v>20</v>
+      </c>
+      <c r="N13">
+        <f>MIN(N6:N10)</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B14" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B12">
-        <f>MAX(B4:B8)</f>
-        <v>725</v>
-      </c>
-      <c r="C12">
-        <f t="shared" ref="C12:M12" si="4">MAX(C4:C8)</f>
-        <v>725</v>
-      </c>
-      <c r="D12">
-        <f t="shared" si="4"/>
-        <v>725</v>
-      </c>
-      <c r="E12">
-        <f t="shared" si="4"/>
-        <v>725</v>
-      </c>
-      <c r="F12">
-        <f t="shared" si="4"/>
-        <v>725</v>
-      </c>
-      <c r="G12">
-        <f t="shared" si="4"/>
-        <v>725</v>
-      </c>
-      <c r="H12">
-        <f t="shared" si="4"/>
-        <v>725</v>
-      </c>
-      <c r="I12">
-        <f t="shared" si="4"/>
-        <v>725</v>
-      </c>
-      <c r="J12">
-        <f t="shared" si="4"/>
-        <v>725</v>
-      </c>
-      <c r="K12">
-        <f t="shared" si="4"/>
-        <v>725</v>
-      </c>
-      <c r="L12">
-        <f t="shared" si="4"/>
-        <v>725</v>
-      </c>
-      <c r="M12">
-        <f t="shared" si="4"/>
-        <v>725</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
+      <c r="C14">
+        <f>MAX(C6:C10)</f>
+        <v>725</v>
+      </c>
+      <c r="D14">
+        <f>MAX(D6:D10)</f>
+        <v>725</v>
+      </c>
+      <c r="E14">
+        <f>MAX(E6:E10)</f>
+        <v>725</v>
+      </c>
+      <c r="F14">
+        <f>MAX(F6:F10)</f>
+        <v>725</v>
+      </c>
+      <c r="G14">
+        <f>MAX(G6:G10)</f>
+        <v>725</v>
+      </c>
+      <c r="H14">
+        <f>MAX(H6:H10)</f>
+        <v>725</v>
+      </c>
+      <c r="I14">
+        <f>MAX(I6:I10)</f>
+        <v>725</v>
+      </c>
+      <c r="J14">
+        <f>MAX(J6:J10)</f>
+        <v>725</v>
+      </c>
+      <c r="K14">
+        <f>MAX(K6:K10)</f>
+        <v>725</v>
+      </c>
+      <c r="L14">
+        <f>MAX(L6:L10)</f>
+        <v>725</v>
+      </c>
+      <c r="M14">
+        <f>MAX(M6:M10)</f>
+        <v>725</v>
+      </c>
+      <c r="N14">
+        <f>MAX(N6:N10)</f>
+        <v>725</v>
+      </c>
+    </row>
+    <row r="15" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B15" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B13">
-        <f>AVERAGE(B4:B8)</f>
+      <c r="C15">
+        <f>AVERAGE(C6:C10)</f>
         <v>312</v>
       </c>
-      <c r="C13">
-        <f t="shared" ref="C13:M13" si="5">AVERAGE(C4:C8)</f>
+      <c r="D15">
+        <f>AVERAGE(D6:D10)</f>
         <v>323</v>
       </c>
-      <c r="D13">
-        <f t="shared" si="5"/>
+      <c r="E15">
+        <f>AVERAGE(E6:E10)</f>
         <v>312</v>
       </c>
-      <c r="E13">
-        <f t="shared" si="5"/>
+      <c r="F15">
+        <f>AVERAGE(F6:F10)</f>
         <v>314</v>
       </c>
-      <c r="F13">
-        <f t="shared" si="5"/>
+      <c r="G15">
+        <f>AVERAGE(G6:G10)</f>
         <v>248</v>
       </c>
-      <c r="G13">
-        <f t="shared" si="5"/>
+      <c r="H15">
+        <f>AVERAGE(H6:H10)</f>
         <v>239</v>
       </c>
-      <c r="H13">
-        <f t="shared" si="5"/>
+      <c r="I15">
+        <f>AVERAGE(I6:I10)</f>
         <v>247.4</v>
       </c>
-      <c r="I13">
-        <f t="shared" si="5"/>
+      <c r="J15">
+        <f>AVERAGE(J6:J10)</f>
         <v>227.6</v>
       </c>
-      <c r="J13">
-        <f t="shared" si="5"/>
+      <c r="K15">
+        <f>AVERAGE(K6:K10)</f>
         <v>236</v>
       </c>
-      <c r="K13">
-        <f t="shared" si="5"/>
+      <c r="L15">
+        <f>AVERAGE(L6:L10)</f>
         <v>244.8</v>
       </c>
-      <c r="L13">
-        <f t="shared" si="5"/>
+      <c r="M15">
+        <f>AVERAGE(M6:M10)</f>
         <v>231</v>
       </c>
-      <c r="M13">
-        <f t="shared" si="5"/>
+      <c r="N15">
+        <f>AVERAGE(N6:N10)</f>
         <v>261</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="16.2" x14ac:dyDescent="0.3">
-      <c r="B16" s="4" t="s">
+    <row r="16" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B16" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16">
+        <f>COUNT(C6:C10)</f>
+        <v>5</v>
+      </c>
+      <c r="D16">
+        <f>COUNT(D6:D10)</f>
+        <v>5</v>
+      </c>
+      <c r="E16">
+        <f>COUNT(E6:E10)</f>
+        <v>5</v>
+      </c>
+      <c r="F16">
+        <f>COUNT(F6:F10)</f>
+        <v>5</v>
+      </c>
+      <c r="G16">
+        <f>COUNT(G6:G10)</f>
+        <v>5</v>
+      </c>
+      <c r="H16">
+        <f>COUNT(H6:H10)</f>
+        <v>5</v>
+      </c>
+      <c r="I16">
+        <f>COUNT(I6:I10)</f>
+        <v>5</v>
+      </c>
+      <c r="J16">
+        <f>COUNT(J6:J10)</f>
+        <v>5</v>
+      </c>
+      <c r="K16">
+        <f>COUNT(K6:K10)</f>
+        <v>5</v>
+      </c>
+      <c r="L16">
+        <f>COUNT(L6:L10)</f>
+        <v>5</v>
+      </c>
+      <c r="M16">
+        <f>COUNT(M6:M10)</f>
+        <v>5</v>
+      </c>
+      <c r="N16">
+        <f>COUNT(N6:N10)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="3:4" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="C18" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="2">
+      <c r="D18" s="2">
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="2:3" ht="16.2" x14ac:dyDescent="0.3">
-      <c r="B17" s="4" t="s">
+    <row r="19" spans="3:4" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="C19" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="2">
+      <c r="D19" s="2">
         <v>150</v>
       </c>
     </row>
-    <row r="18" spans="2:3" ht="16.2" x14ac:dyDescent="0.3">
-      <c r="B18" s="4" t="s">
+    <row r="20" spans="3:4" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="C20" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="2">
+      <c r="D20" s="2">
         <v>55</v>
       </c>
     </row>
-    <row r="19" spans="2:3" ht="16.2" x14ac:dyDescent="0.3">
-      <c r="B19" s="4" t="s">
+    <row r="21" spans="3:4" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="C21" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="2">
-        <f>SUM(C16:C18)</f>
+      <c r="D21" s="2">
+        <f>SUM(D18:D20)</f>
         <v>305</v>
       </c>
     </row>
-    <row r="20" spans="2:3" ht="16.2" x14ac:dyDescent="0.3">
-      <c r="B20" s="4" t="s">
+    <row r="22" spans="3:4" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="C22" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="3">
+      <c r="D22" s="3">
         <v>0.08</v>
       </c>
     </row>
-    <row r="21" spans="2:3" ht="16.2" x14ac:dyDescent="0.3">
-      <c r="B21" s="4" t="s">
+    <row r="23" spans="3:4" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="C23" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="2">
-        <f>C19*(C20+1)</f>
+      <c r="D23" s="2">
+        <f>D21*(D22+1)</f>
         <v>329.40000000000003</v>
       </c>
     </row>
@@ -1059,4 +1112,13 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2EABFB2-A23D-41E9-929A-A2B68F87AB0C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Udemy Excel 101.xlsx
+++ b/Udemy Excel 101.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8EF12D157D92B731/Documents/GitHub/Robert-Rookie-project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="92" documentId="8_{8761CF19-0046-4715-B8FB-9230E793B6F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3A28C96-3F1C-4F57-9E56-9EBFDDF4DE28}"/>
+  <xr:revisionPtr revIDLastSave="110" documentId="8_{8761CF19-0046-4715-B8FB-9230E793B6F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91F2F710-8DC6-4325-8D86-068525FB7CDF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F602598-B120-46E6-997C-287E091787E5}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
   <si>
     <t>Monthly Budget</t>
   </si>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>Counts</t>
+  </si>
+  <si>
+    <t>Water</t>
   </si>
 </sst>
 </file>
@@ -166,6 +169,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -485,11 +492,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2E5EBEE-2860-4ED5-9D0E-88B7E3B3261C}">
-  <dimension ref="B3:P23"/>
+  <dimension ref="B3:P24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" customWidth="1"/>
-    <col min="2" max="13" width="12.77734375" customWidth="1"/>
+    <col min="2" max="2" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.21875" customWidth="1"/>
+    <col min="6" max="6" width="12" hidden="1" customWidth="1"/>
+    <col min="7" max="14" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:16" x14ac:dyDescent="0.3">
@@ -589,8 +600,8 @@
         <v>8700</v>
       </c>
       <c r="P6">
-        <f>O6/$O$11</f>
-        <v>0.54446460980036293</v>
+        <f>O6/$O$12</f>
+        <v>0.52858618385078071</v>
       </c>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.3">
@@ -638,8 +649,8 @@
         <v>240</v>
       </c>
       <c r="P7">
-        <f>O7/$O$11</f>
-        <v>1.5019713373803117E-2</v>
+        <f>O7/$O$12</f>
+        <v>1.4581687830366365E-2</v>
       </c>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.3">
@@ -687,430 +698,482 @@
         <v>1725</v>
       </c>
       <c r="P8">
-        <f>O8/$O$11</f>
-        <v>0.1079541898742099</v>
+        <f>O8/$O$12</f>
+        <v>0.10480588128075825</v>
       </c>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C9">
-        <v>400</v>
+        <v>40</v>
       </c>
       <c r="D9">
-        <v>450</v>
+        <v>40</v>
       </c>
       <c r="E9">
-        <v>400</v>
+        <v>40</v>
       </c>
       <c r="F9">
-        <v>400</v>
+        <v>40</v>
       </c>
       <c r="G9">
-        <v>450</v>
+        <v>40</v>
       </c>
       <c r="H9">
-        <v>400</v>
+        <v>40</v>
       </c>
       <c r="I9">
-        <v>450</v>
+        <v>40</v>
       </c>
       <c r="J9">
-        <v>350</v>
+        <v>40</v>
       </c>
       <c r="K9">
-        <v>400</v>
+        <v>40</v>
       </c>
       <c r="L9">
-        <v>450</v>
+        <v>40</v>
       </c>
       <c r="M9">
-        <v>350</v>
+        <v>40</v>
       </c>
       <c r="N9">
-        <v>450</v>
+        <v>40</v>
       </c>
       <c r="O9">
         <f>SUM(C9:N9)</f>
-        <v>4950</v>
+        <v>480</v>
       </c>
       <c r="P9">
-        <f>O9/$O$11</f>
-        <v>0.30978158833468927</v>
+        <f>O9/$O$12</f>
+        <v>2.9163375660732731E-2</v>
       </c>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10">
-        <v>15</v>
+        <v>400</v>
       </c>
       <c r="D10">
-        <v>20</v>
+        <v>450</v>
       </c>
       <c r="E10">
-        <v>15</v>
+        <v>400</v>
       </c>
       <c r="F10">
-        <v>25</v>
+        <v>400</v>
       </c>
       <c r="G10">
-        <v>35</v>
+        <v>450</v>
       </c>
       <c r="H10">
-        <v>45</v>
+        <v>400</v>
       </c>
       <c r="I10">
-        <v>25</v>
+        <v>450</v>
       </c>
       <c r="J10">
-        <v>35</v>
+        <v>350</v>
       </c>
       <c r="K10">
-        <v>25</v>
+        <v>400</v>
       </c>
       <c r="L10">
-        <v>14</v>
+        <v>450</v>
       </c>
       <c r="M10">
-        <v>35</v>
+        <v>350</v>
       </c>
       <c r="N10">
-        <v>75</v>
+        <v>450</v>
       </c>
       <c r="O10">
         <f>SUM(C10:N10)</f>
-        <v>364</v>
+        <v>4950</v>
       </c>
       <c r="P10">
-        <f>O10/$O$11</f>
-        <v>2.2779898616934725E-2</v>
+        <f>O10/$O$12</f>
+        <v>0.30074731150130629</v>
       </c>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C11">
-        <f>SUM(C6:C10)</f>
-        <v>1560</v>
+        <v>15</v>
       </c>
       <c r="D11">
-        <f>SUM(D6:D10)</f>
-        <v>1615</v>
+        <v>20</v>
       </c>
       <c r="E11">
-        <f>SUM(E6:E10)</f>
-        <v>1560</v>
+        <v>15</v>
       </c>
       <c r="F11">
-        <f>SUM(F6:F10)</f>
-        <v>1570</v>
+        <v>25</v>
       </c>
       <c r="G11">
-        <f>SUM(G6:G10)</f>
-        <v>1240</v>
+        <v>35</v>
       </c>
       <c r="H11">
-        <f>SUM(H6:H10)</f>
-        <v>1195</v>
+        <v>45</v>
       </c>
       <c r="I11">
-        <f>SUM(I6:I10)</f>
-        <v>1237</v>
+        <v>25</v>
       </c>
       <c r="J11">
-        <f>SUM(J6:J10)</f>
-        <v>1138</v>
+        <v>35</v>
       </c>
       <c r="K11">
-        <f>SUM(K6:K10)</f>
-        <v>1180</v>
+        <v>25</v>
       </c>
       <c r="L11">
-        <f>SUM(L6:L10)</f>
-        <v>1224</v>
+        <v>14</v>
       </c>
       <c r="M11">
-        <f>SUM(M6:M10)</f>
-        <v>1155</v>
+        <v>35</v>
       </c>
       <c r="N11">
-        <f>SUM(N6:N10)</f>
-        <v>1305</v>
+        <v>75</v>
       </c>
       <c r="O11">
         <f>SUM(C11:N11)</f>
-        <v>15979</v>
-      </c>
-    </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13">
-        <f>MIN(C6:C10)</f>
-        <v>15</v>
-      </c>
-      <c r="D13">
-        <f>MIN(D6:D10)</f>
-        <v>20</v>
-      </c>
-      <c r="E13">
-        <f>MIN(E6:E10)</f>
-        <v>15</v>
-      </c>
-      <c r="F13">
-        <f>MIN(F6:F10)</f>
-        <v>20</v>
-      </c>
-      <c r="G13">
-        <f>MIN(G6:G10)</f>
-        <v>10</v>
-      </c>
-      <c r="H13">
-        <f>MIN(H6:H10)</f>
-        <v>5</v>
-      </c>
-      <c r="I13">
-        <f>MIN(I6:I10)</f>
-        <v>17</v>
-      </c>
-      <c r="J13">
-        <f>MIN(J6:J10)</f>
-        <v>8</v>
-      </c>
-      <c r="K13">
-        <f>MIN(K6:K10)</f>
-        <v>10</v>
-      </c>
-      <c r="L13">
-        <f>MIN(L6:L10)</f>
-        <v>14</v>
-      </c>
-      <c r="M13">
-        <f>MIN(M6:M10)</f>
-        <v>20</v>
-      </c>
-      <c r="N13">
-        <f>MIN(N6:N10)</f>
-        <v>20</v>
+        <v>364</v>
+      </c>
+      <c r="P11">
+        <f>O11/$O$12</f>
+        <v>2.2115559876055655E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12">
+        <f>SUM(C6:C11)</f>
+        <v>1600</v>
+      </c>
+      <c r="D12">
+        <f>SUM(D6:D11)</f>
+        <v>1655</v>
+      </c>
+      <c r="E12">
+        <f>SUM(E6:E11)</f>
+        <v>1600</v>
+      </c>
+      <c r="F12">
+        <f>SUM(F6:F11)</f>
+        <v>1610</v>
+      </c>
+      <c r="G12">
+        <f>SUM(G6:G11)</f>
+        <v>1280</v>
+      </c>
+      <c r="H12">
+        <f>SUM(H6:H11)</f>
+        <v>1235</v>
+      </c>
+      <c r="I12">
+        <f>SUM(I6:I11)</f>
+        <v>1277</v>
+      </c>
+      <c r="J12">
+        <f>SUM(J6:J11)</f>
+        <v>1178</v>
+      </c>
+      <c r="K12">
+        <f>SUM(K6:K11)</f>
+        <v>1220</v>
+      </c>
+      <c r="L12">
+        <f>SUM(L6:L11)</f>
+        <v>1264</v>
+      </c>
+      <c r="M12">
+        <f>SUM(M6:M11)</f>
+        <v>1195</v>
+      </c>
+      <c r="N12">
+        <f>SUM(N6:N11)</f>
+        <v>1345</v>
+      </c>
+      <c r="O12">
+        <f>SUM(C12:N12)</f>
+        <v>16459</v>
       </c>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14">
+        <f>MIN(C6:C11)</f>
         <v>15</v>
       </c>
-      <c r="C14">
-        <f>MAX(C6:C10)</f>
-        <v>725</v>
-      </c>
       <c r="D14">
-        <f>MAX(D6:D10)</f>
-        <v>725</v>
+        <f>MIN(D6:D11)</f>
+        <v>20</v>
       </c>
       <c r="E14">
-        <f>MAX(E6:E10)</f>
-        <v>725</v>
+        <f>MIN(E6:E11)</f>
+        <v>15</v>
       </c>
       <c r="F14">
-        <f>MAX(F6:F10)</f>
-        <v>725</v>
+        <f>MIN(F6:F11)</f>
+        <v>20</v>
       </c>
       <c r="G14">
-        <f>MAX(G6:G10)</f>
-        <v>725</v>
+        <f>MIN(G6:G11)</f>
+        <v>10</v>
       </c>
       <c r="H14">
-        <f>MAX(H6:H10)</f>
-        <v>725</v>
+        <f>MIN(H6:H11)</f>
+        <v>5</v>
       </c>
       <c r="I14">
-        <f>MAX(I6:I10)</f>
-        <v>725</v>
+        <f>MIN(I6:I11)</f>
+        <v>17</v>
       </c>
       <c r="J14">
-        <f>MAX(J6:J10)</f>
-        <v>725</v>
+        <f>MIN(J6:J11)</f>
+        <v>8</v>
       </c>
       <c r="K14">
-        <f>MAX(K6:K10)</f>
-        <v>725</v>
+        <f>MIN(K6:K11)</f>
+        <v>10</v>
       </c>
       <c r="L14">
-        <f>MAX(L6:L10)</f>
-        <v>725</v>
+        <f>MIN(L6:L11)</f>
+        <v>14</v>
       </c>
       <c r="M14">
-        <f>MAX(M6:M10)</f>
-        <v>725</v>
+        <f>MIN(M6:M11)</f>
+        <v>20</v>
       </c>
       <c r="N14">
-        <f>MAX(N6:N10)</f>
-        <v>725</v>
+        <f>MIN(N6:N11)</f>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B15" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C15">
-        <f>AVERAGE(C6:C10)</f>
-        <v>312</v>
+        <f>MAX(C6:C11)</f>
+        <v>725</v>
       </c>
       <c r="D15">
-        <f>AVERAGE(D6:D10)</f>
-        <v>323</v>
+        <f>MAX(D6:D11)</f>
+        <v>725</v>
       </c>
       <c r="E15">
-        <f>AVERAGE(E6:E10)</f>
-        <v>312</v>
+        <f>MAX(E6:E11)</f>
+        <v>725</v>
       </c>
       <c r="F15">
-        <f>AVERAGE(F6:F10)</f>
-        <v>314</v>
+        <f>MAX(F6:F11)</f>
+        <v>725</v>
       </c>
       <c r="G15">
-        <f>AVERAGE(G6:G10)</f>
-        <v>248</v>
+        <f>MAX(G6:G11)</f>
+        <v>725</v>
       </c>
       <c r="H15">
-        <f>AVERAGE(H6:H10)</f>
-        <v>239</v>
+        <f>MAX(H6:H11)</f>
+        <v>725</v>
       </c>
       <c r="I15">
-        <f>AVERAGE(I6:I10)</f>
-        <v>247.4</v>
+        <f>MAX(I6:I11)</f>
+        <v>725</v>
       </c>
       <c r="J15">
-        <f>AVERAGE(J6:J10)</f>
-        <v>227.6</v>
+        <f>MAX(J6:J11)</f>
+        <v>725</v>
       </c>
       <c r="K15">
-        <f>AVERAGE(K6:K10)</f>
-        <v>236</v>
+        <f>MAX(K6:K11)</f>
+        <v>725</v>
       </c>
       <c r="L15">
-        <f>AVERAGE(L6:L10)</f>
-        <v>244.8</v>
+        <f>MAX(L6:L11)</f>
+        <v>725</v>
       </c>
       <c r="M15">
-        <f>AVERAGE(M6:M10)</f>
-        <v>231</v>
+        <f>MAX(M6:M11)</f>
+        <v>725</v>
       </c>
       <c r="N15">
-        <f>AVERAGE(N6:N10)</f>
-        <v>261</v>
+        <f>MAX(N6:N11)</f>
+        <v>725</v>
       </c>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B16" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16">
+        <f>AVERAGE(C6:C11)</f>
+        <v>266.66666666666669</v>
+      </c>
+      <c r="D16">
+        <f>AVERAGE(D6:D11)</f>
+        <v>275.83333333333331</v>
+      </c>
+      <c r="E16">
+        <f>AVERAGE(E6:E11)</f>
+        <v>266.66666666666669</v>
+      </c>
+      <c r="F16">
+        <f>AVERAGE(F6:F11)</f>
+        <v>268.33333333333331</v>
+      </c>
+      <c r="G16">
+        <f>AVERAGE(G6:G11)</f>
+        <v>213.33333333333334</v>
+      </c>
+      <c r="H16">
+        <f>AVERAGE(H6:H11)</f>
+        <v>205.83333333333334</v>
+      </c>
+      <c r="I16">
+        <f>AVERAGE(I6:I11)</f>
+        <v>212.83333333333334</v>
+      </c>
+      <c r="J16">
+        <f>AVERAGE(J6:J11)</f>
+        <v>196.33333333333334</v>
+      </c>
+      <c r="K16">
+        <f>AVERAGE(K6:K11)</f>
+        <v>203.33333333333334</v>
+      </c>
+      <c r="L16">
+        <f>AVERAGE(L6:L11)</f>
+        <v>210.66666666666666</v>
+      </c>
+      <c r="M16">
+        <f>AVERAGE(M6:M11)</f>
+        <v>199.16666666666666</v>
+      </c>
+      <c r="N16">
+        <f>AVERAGE(N6:N11)</f>
+        <v>224.16666666666666</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B17" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C16">
-        <f>COUNT(C6:C10)</f>
-        <v>5</v>
-      </c>
-      <c r="D16">
-        <f>COUNT(D6:D10)</f>
-        <v>5</v>
-      </c>
-      <c r="E16">
-        <f>COUNT(E6:E10)</f>
-        <v>5</v>
-      </c>
-      <c r="F16">
-        <f>COUNT(F6:F10)</f>
-        <v>5</v>
-      </c>
-      <c r="G16">
-        <f>COUNT(G6:G10)</f>
-        <v>5</v>
-      </c>
-      <c r="H16">
-        <f>COUNT(H6:H10)</f>
-        <v>5</v>
-      </c>
-      <c r="I16">
-        <f>COUNT(I6:I10)</f>
-        <v>5</v>
-      </c>
-      <c r="J16">
-        <f>COUNT(J6:J10)</f>
-        <v>5</v>
-      </c>
-      <c r="K16">
-        <f>COUNT(K6:K10)</f>
-        <v>5</v>
-      </c>
-      <c r="L16">
-        <f>COUNT(L6:L10)</f>
-        <v>5</v>
-      </c>
-      <c r="M16">
-        <f>COUNT(M6:M10)</f>
-        <v>5</v>
-      </c>
-      <c r="N16">
-        <f>COUNT(N6:N10)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="3:4" ht="16.2" x14ac:dyDescent="0.3">
-      <c r="C18" s="4" t="s">
+      <c r="C17">
+        <f t="shared" ref="C17:N17" si="0">COUNT(C6:C11)</f>
+        <v>6</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="L17">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="M17">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="N17">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="C19" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D19" s="2">
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="3:4" ht="16.2" x14ac:dyDescent="0.3">
-      <c r="C19" s="4" t="s">
+    <row r="20" spans="2:14" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="C20" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D20" s="2">
         <v>150</v>
       </c>
     </row>
-    <row r="20" spans="3:4" ht="16.2" x14ac:dyDescent="0.3">
-      <c r="C20" s="4" t="s">
+    <row r="21" spans="2:14" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="C21" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D21" s="2">
         <v>55</v>
       </c>
     </row>
-    <row r="21" spans="3:4" ht="16.2" x14ac:dyDescent="0.3">
-      <c r="C21" s="4" t="s">
+    <row r="22" spans="2:14" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="C22" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D21" s="2">
-        <f>SUM(D18:D20)</f>
+      <c r="D22" s="2">
+        <f>SUM(D19:D21)</f>
         <v>305</v>
       </c>
     </row>
-    <row r="22" spans="3:4" ht="16.2" x14ac:dyDescent="0.3">
-      <c r="C22" s="4" t="s">
+    <row r="23" spans="2:14" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="C23" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D23" s="3">
         <v>0.08</v>
       </c>
     </row>
-    <row r="23" spans="3:4" ht="16.2" x14ac:dyDescent="0.3">
-      <c r="C23" s="4" t="s">
+    <row r="24" spans="2:14" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="C24" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D23" s="2">
-        <f>D21*(D22+1)</f>
+      <c r="D24" s="2">
+        <f>D22*(D23+1)</f>
         <v>329.40000000000003</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="C12:N17" formulaRange="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 

--- a/Udemy Excel 101.xlsx
+++ b/Udemy Excel 101.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8EF12D157D92B731/Documents/GitHub/Robert-Rookie-project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="225" documentId="8_{8761CF19-0046-4715-B8FB-9230E793B6F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{432DDBC1-3C89-400A-BE46-DC17185A7CE0}"/>
+  <xr:revisionPtr revIDLastSave="321" documentId="8_{8761CF19-0046-4715-B8FB-9230E793B6F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B7C5391-5B0E-4154-882A-F0A08D3AC642}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F602598-B120-46E6-997C-287E091787E5}"/>
   </bookViews>
   <sheets>
     <sheet name="Budget " sheetId="7" r:id="rId1"/>
+    <sheet name="Chart Monthly Budget" sheetId="8" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,9 +38,6 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
-  <si>
-    <t>Monthly Budget</t>
-  </si>
   <si>
     <t>Bills</t>
   </si>
@@ -94,6 +92,9 @@
   <si>
     <t>Water</t>
   </si>
+  <si>
+    <t xml:space="preserve"> 2025 Monthly Budget</t>
+  </si>
 </sst>
 </file>
 
@@ -105,7 +106,7 @@
     <numFmt numFmtId="164" formatCode="mmm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="_-[$€-2]\ * #,##0.00_-;\-[$€-2]\ * #,##0.00_-;_-[$€-2]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -156,6 +157,13 @@
       <color theme="3" tint="-0.249977111117893"/>
       <name val="Verdana"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Tw Cen MT"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -233,17 +241,11 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyNumberFormat="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -252,6 +254,13 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -281,18 +290,5417 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="2000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:view3D>
+      <c:rotX val="50"/>
+      <c:rotY val="0"/>
+      <c:depthPercent val="100"/>
+      <c:rAngAx val="0"/>
+    </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:backWall>
+    <c:plotArea>
+      <c:layout/>
+      <c:pie3DChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Budget '!$E$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Feb-2025</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:sp3d/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001E-C9DD-47FD-A720-C2D00CDAFA87}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:sp3d/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001F-C9DD-47FD-A720-C2D00CDAFA87}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:sp3d/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000020-C9DD-47FD-A720-C2D00CDAFA87}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:sp3d/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000021-C9DD-47FD-A720-C2D00CDAFA87}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:sp3d/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000022-C9DD-47FD-A720-C2D00CDAFA87}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:sp3d/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000023-C9DD-47FD-A720-C2D00CDAFA87}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.16462976593292347"/>
+                  <c:y val="3.3033687913746446E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="bestFit"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000001E-C9DD-47FD-A720-C2D00CDAFA87}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.12752604814781474"/>
+                  <c:y val="-0.2814267006264809"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="bestFit"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000020-C9DD-47FD-A720-C2D00CDAFA87}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.15122734742219093"/>
+                  <c:y val="0.11157158473584036"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="bestFit"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000022-C9DD-47FD-A720-C2D00CDAFA87}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:pattFill prst="pct75">
+                <a:fgClr>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="inEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="1"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="50000"/>
+                      <a:lumOff val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Budget '!$C$5:$C$10</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Rent</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Phone </c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Credit Cards</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Water</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Food</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Candy</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Budget '!$E$5:$E$10</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0" formatCode="_-[$€-2]\ * #,##0.00_-;\-[$€-2]\ * #,##0.00_-;_-[$€-2]\ * &quot;-&quot;??_-;_-@_-">
+                  <c:v>725</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C9DD-47FD-A720-C2D00CDAFA87}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+      </c:pie3DChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="39000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr rtl="0">
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="lt1"/>
+        </a:gs>
+        <a:gs pos="39000">
+          <a:schemeClr val="lt1"/>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="lt1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="25000"/>
+          <a:lumOff val="75000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:strRef>
+          <c:f>'Budget '!$C$2:$O$2</c:f>
+          <c:strCache>
+            <c:ptCount val="13"/>
+            <c:pt idx="0">
+              <c:v> 2025 Monthly Budget</c:v>
+            </c:pt>
+          </c:strCache>
+        </c:strRef>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mj-lt"/>
+              <a:ea typeface="+mj-ea"/>
+              <a:cs typeface="+mj-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Budget '!$C$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Rent</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000006-D68D-45F9-BB30-C601C56B202C}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Budget '!$D$4:$O$4</c:f>
+              <c:numCache>
+                <c:formatCode>mmm\-yyyy</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>45658</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>45689</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45717</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45748</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45778</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>45809</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>45839</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>45870</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>45901</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>45931</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>45962</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>45992</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Budget '!$D$5:$O$5</c:f>
+              <c:numCache>
+                <c:formatCode>_-[$€-2]\ * #,##0.00_-;\-[$€-2]\ * #,##0.00_-;_-[$€-2]\ * "-"??_-;_-@_-</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>725</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>725</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>725</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>725</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>725</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>725</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>725</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>725</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>725</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>725</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>725</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>725</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D68D-45F9-BB30-C601C56B202C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Budget '!$C$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Phone </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Budget '!$D$4:$O$4</c:f>
+              <c:numCache>
+                <c:formatCode>mmm\-yyyy</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>45658</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>45689</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45717</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45748</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45778</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>45809</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>45839</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>45870</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>45901</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>45931</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>45962</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>45992</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Budget '!$D$6:$O$6</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-D68D-45F9-BB30-C601C56B202C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Budget '!$C$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Credit Cards</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Budget '!$D$4:$O$4</c:f>
+              <c:numCache>
+                <c:formatCode>mmm\-yyyy</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>45658</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>45689</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45717</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45748</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45778</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>45809</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>45839</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>45870</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>45901</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>45931</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>45962</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>45992</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Budget '!$D$7:$O$7</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>35</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-D68D-45F9-BB30-C601C56B202C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Budget '!$C$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Water</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Budget '!$D$4:$O$4</c:f>
+              <c:numCache>
+                <c:formatCode>mmm\-yyyy</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>45658</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>45689</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45717</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45748</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45778</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>45809</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>45839</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>45870</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>45901</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>45931</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>45962</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>45992</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Budget '!$D$8:$O$8</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>40</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-D68D-45F9-BB30-C601C56B202C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Budget '!$C$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Food</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Budget '!$D$4:$O$4</c:f>
+              <c:numCache>
+                <c:formatCode>mmm\-yyyy</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>45658</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>45689</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45717</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45748</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45778</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>45809</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>45839</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>45870</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>45901</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>45931</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>45962</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>45992</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Budget '!$D$9:$O$9</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>350</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>350</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>450</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-D68D-45F9-BB30-C601C56B202C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Budget '!$C$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Candy</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Budget '!$D$4:$O$4</c:f>
+              <c:numCache>
+                <c:formatCode>mmm\-yyyy</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>45658</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>45689</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45717</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45748</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45778</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>45809</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>45839</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>45870</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>45901</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>45931</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>45962</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>45992</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Budget '!$D$10:$O$10</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>75</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-D68D-45F9-BB30-C601C56B202C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="199"/>
+        <c:axId val="376643984"/>
+        <c:axId val="84368496"/>
+      </c:barChart>
+      <c:dateAx>
+        <c:axId val="376643984"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="mmm\-yyyy" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="84368496"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="months"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="84368496"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:numFmt formatCode="_-[$€-2]\ * #,##0.00_-;\-[$€-2]\ * #,##0.00_-;_-[$€-2]\ * &quot;-&quot;??_-;_-@_-" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="376643984"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="12">
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="264">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200" cap="all" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="39000">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="lt1">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="pct75">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:bgClr>
+      </a:pattFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+    <cs:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="pct75">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:bgClr>
+      </a:pattFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+    <cs:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="20000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="20000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
+                <a:alpha val="42000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="75000"/>
+                <a:alpha val="36000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
+                <a:alpha val="42000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="75000"/>
+                <a:alpha val="36000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+          <a:alpha val="39000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1800" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="212">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" b="0" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="38100" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="8"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="major">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="2000" b="0" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/chartsheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{A517E6B5-41BB-4526-8940-91D07FE77E74}">
+  <sheetPr/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</chartsheet>
+</file>
+
+<file path=xl/diagrams/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<dgm:colorsDef xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uniqueId="urn:microsoft.com/office/officeart/2005/8/colors/accent1_2">
+  <dgm:title val=""/>
+  <dgm:desc val=""/>
+  <dgm:catLst>
+    <dgm:cat type="accent1" pri="11200"/>
+  </dgm:catLst>
+  <dgm:styleLbl name="node0">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent1"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="alignNode1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent1"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="node1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent1"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="lnNode1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent1"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="vennNode1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent1">
+        <a:alpha val="50000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="node2">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent1"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="node3">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent1"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="node4">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent1"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgImgPlace1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent1">
+        <a:tint val="50000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="alignImgPlace1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent1">
+        <a:tint val="50000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="bgImgPlace1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent1">
+        <a:tint val="50000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="sibTrans2D1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent1">
+        <a:tint val="60000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent1">
+        <a:tint val="60000"/>
+      </a:schemeClr>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgSibTrans2D1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent1">
+        <a:tint val="60000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent1">
+        <a:tint val="60000"/>
+      </a:schemeClr>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="bgSibTrans2D1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent1">
+        <a:tint val="60000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent1">
+        <a:tint val="60000"/>
+      </a:schemeClr>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="sibTrans1D1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent1"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="tx1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="callout">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent1"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent1">
+        <a:tint val="50000"/>
+      </a:schemeClr>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="tx1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="asst0">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent1"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="asst1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent1"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="asst2">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent1"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="asst3">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent1"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="asst4">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent1"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans2D1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent1">
+        <a:tint val="60000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent1">
+        <a:tint val="60000"/>
+      </a:schemeClr>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans2D2">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent1"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans2D3">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent1"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans2D4">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent1"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans1D1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent1"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent1">
+        <a:shade val="60000"/>
+      </a:schemeClr>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="tx1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans1D2">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent1"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent1">
+        <a:shade val="60000"/>
+      </a:schemeClr>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="tx1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans1D3">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent1"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent1">
+        <a:shade val="80000"/>
+      </a:schemeClr>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="tx1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans1D4">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent1"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent1">
+        <a:shade val="80000"/>
+      </a:schemeClr>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="tx1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgAcc1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="lt1">
+        <a:alpha val="90000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="conFgAcc1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="lt1">
+        <a:alpha val="90000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="alignAcc1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="lt1">
+        <a:alpha val="90000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="trAlignAcc1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="lt1">
+        <a:alpha val="40000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="bgAcc1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="lt1">
+        <a:alpha val="90000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="solidFgAcc1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="solidAlignAcc1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="solidBgAcc1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgAccFollowNode1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent1">
+        <a:alpha val="90000"/>
+        <a:tint val="40000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent1">
+        <a:alpha val="90000"/>
+        <a:tint val="40000"/>
+      </a:schemeClr>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="alignAccFollowNode1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent1">
+        <a:alpha val="90000"/>
+        <a:tint val="40000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent1">
+        <a:alpha val="90000"/>
+        <a:tint val="40000"/>
+      </a:schemeClr>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="bgAccFollowNode1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent1">
+        <a:alpha val="90000"/>
+        <a:tint val="40000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent1">
+        <a:alpha val="90000"/>
+        <a:tint val="40000"/>
+      </a:schemeClr>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgAcc0">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="lt1">
+        <a:alpha val="90000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgAcc2">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="lt1">
+        <a:alpha val="90000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgAcc3">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="lt1">
+        <a:alpha val="90000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgAcc4">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="lt1">
+        <a:alpha val="90000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="bgShp">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent1">
+        <a:tint val="40000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="dkBgShp">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent1">
+        <a:shade val="80000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="trBgShp">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent1">
+        <a:tint val="50000"/>
+        <a:alpha val="40000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgShp">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent1">
+        <a:tint val="60000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="revTx">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="lt1">
+        <a:alpha val="0"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="dk1">
+        <a:alpha val="0"/>
+      </a:schemeClr>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="tx1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+</dgm:colorsDef>
+</file>
+
+<file path=xl/diagrams/data1.xml><?xml version="1.0" encoding="utf-8"?>
+<dgm:dataModel xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <dgm:ptLst>
+    <dgm:pt modelId="{F49C658C-10D3-4771-BEEA-9451B8942588}" type="doc">
+      <dgm:prSet loTypeId="urn:microsoft.com/office/officeart/2005/8/layout/hProcess9" loCatId="process" qsTypeId="urn:microsoft.com/office/officeart/2005/8/quickstyle/simple1" qsCatId="simple" csTypeId="urn:microsoft.com/office/officeart/2005/8/colors/accent1_2" csCatId="accent1" phldr="1"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{A80E0E70-3605-43C1-896B-9E0E2DA76989}">
+      <dgm:prSet phldrT="[Text]"/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IE"/>
+            <a:t>Make Money</a:t>
+          </a:r>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{043BDE8D-8156-41E6-8A4F-E9FA440DDBFD}" type="parTrans" cxnId="{5A30BAE3-97B7-4F01-80BE-AF1EFD64FEDB}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="en-IE"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{5EA87B87-D2EC-4939-953D-A5B1B33D8508}" type="sibTrans" cxnId="{5A30BAE3-97B7-4F01-80BE-AF1EFD64FEDB}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="en-IE"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{07D39319-F6E7-4B32-8B52-F78600763031}">
+      <dgm:prSet phldrT="[Text]"/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IE"/>
+            <a:t>Spend Money</a:t>
+          </a:r>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{06B09E15-DAFE-4287-BC51-34DA9409AC51}" type="parTrans" cxnId="{1FFE1FC8-FA3A-4625-9B28-E892EDBAB31C}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="en-IE"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{A035C452-63CD-4181-890B-1FF929F042A3}" type="sibTrans" cxnId="{1FFE1FC8-FA3A-4625-9B28-E892EDBAB31C}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="en-IE"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{6E31ABEB-3664-4065-A90E-022334D1CA1B}">
+      <dgm:prSet phldrT="[Text]"/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IE"/>
+            <a:t>Track Money</a:t>
+          </a:r>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{3367770C-714A-4F20-9B4D-629D5F9916B1}" type="parTrans" cxnId="{9345E2B9-12C8-42C1-980F-4D1E95F22408}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="en-IE"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{52DE96E7-F507-40BD-8510-6294B772A5B5}" type="sibTrans" cxnId="{9345E2B9-12C8-42C1-980F-4D1E95F22408}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="en-IE"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{D51B010A-3DEB-400F-8603-09D23BDF844C}">
+      <dgm:prSet phldrT="[Text]"/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IE"/>
+            <a:t> Work</a:t>
+          </a:r>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{656E1BE1-D482-4598-A79D-C5541D65E632}" type="parTrans" cxnId="{9B3AE875-6892-497B-8A80-12DEB50BE70C}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="en-IE"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{189D73AC-6EC1-4E10-A0FE-0AE330FD69C9}" type="sibTrans" cxnId="{9B3AE875-6892-497B-8A80-12DEB50BE70C}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="en-IE"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{019F7FC0-8C7A-47FC-B340-709D6BB4F28C}">
+      <dgm:prSet phldrT="[Text]"/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IE"/>
+            <a:t>Ask my Mom</a:t>
+          </a:r>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{86C45E07-DE6E-4948-B6E8-3578519D54CF}" type="parTrans" cxnId="{4D5D541A-2B93-4624-92B3-D59FA3AC1E73}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="en-IE"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{5F1AC7EC-5765-409E-B136-EE8AAEF13065}" type="sibTrans" cxnId="{4D5D541A-2B93-4624-92B3-D59FA3AC1E73}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="en-IE"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{87DA0775-CFC5-4542-A673-22DA53EE1FB3}">
+      <dgm:prSet phldrT="[Text]"/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IE"/>
+            <a:t>Monthly Fixed Expenses</a:t>
+          </a:r>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{A0F696CE-20F0-46F6-8BA1-339843D73582}" type="parTrans" cxnId="{BA598CB1-815E-4D99-87AC-6D52764CBE92}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="en-IE"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{BE2F7E7D-4ED3-45C8-A4D2-2734A70E1720}" type="sibTrans" cxnId="{BA598CB1-815E-4D99-87AC-6D52764CBE92}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="en-IE"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{55F473C3-FE38-4F89-A48A-F8616C607E64}">
+      <dgm:prSet phldrT="[Text]"/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-IE"/>
+            <a:t>Monthly Variable Expenses</a:t>
+          </a:r>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{C143A2A3-4D38-4F3C-AF0A-B70CFA186F8F}" type="parTrans" cxnId="{B02DA946-26C9-467D-BFA2-27203C1A2EB7}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="en-IE"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{401A0670-2781-4ECB-BBEA-868183E0129D}" type="sibTrans" cxnId="{B02DA946-26C9-467D-BFA2-27203C1A2EB7}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="en-IE"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{F7A8CD19-F803-4157-B6EC-3C39C3F72FAD}" type="pres">
+      <dgm:prSet presAssocID="{F49C658C-10D3-4771-BEEA-9451B8942588}" presName="CompostProcess" presStyleCnt="0">
+        <dgm:presLayoutVars>
+          <dgm:dir/>
+          <dgm:resizeHandles val="exact"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{02BFDC3E-9A59-43F4-B090-534F9CA78771}" type="pres">
+      <dgm:prSet presAssocID="{F49C658C-10D3-4771-BEEA-9451B8942588}" presName="arrow" presStyleLbl="bgShp" presStyleIdx="0" presStyleCnt="1"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{63F0A124-DA13-4157-9743-CDDDBF503FF5}" type="pres">
+      <dgm:prSet presAssocID="{F49C658C-10D3-4771-BEEA-9451B8942588}" presName="linearProcess" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{3199F3B8-5EC2-4F94-976C-2EBE9DEB433A}" type="pres">
+      <dgm:prSet presAssocID="{A80E0E70-3605-43C1-896B-9E0E2DA76989}" presName="textNode" presStyleLbl="node1" presStyleIdx="0" presStyleCnt="3">
+        <dgm:presLayoutVars>
+          <dgm:bulletEnabled val="1"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{5B80FEB3-7CCF-4C21-9372-A1B12C42CC4C}" type="pres">
+      <dgm:prSet presAssocID="{5EA87B87-D2EC-4939-953D-A5B1B33D8508}" presName="sibTrans" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{C75E2687-E3E1-4FB6-A473-6B5A0BA5A8EB}" type="pres">
+      <dgm:prSet presAssocID="{07D39319-F6E7-4B32-8B52-F78600763031}" presName="textNode" presStyleLbl="node1" presStyleIdx="1" presStyleCnt="3">
+        <dgm:presLayoutVars>
+          <dgm:bulletEnabled val="1"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{15BEE5DF-1DEF-4917-A925-79DF5FEC74C0}" type="pres">
+      <dgm:prSet presAssocID="{A035C452-63CD-4181-890B-1FF929F042A3}" presName="sibTrans" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{F1BA3163-B742-47E9-9399-FD9E172DCCD4}" type="pres">
+      <dgm:prSet presAssocID="{6E31ABEB-3664-4065-A90E-022334D1CA1B}" presName="textNode" presStyleLbl="node1" presStyleIdx="2" presStyleCnt="3">
+        <dgm:presLayoutVars>
+          <dgm:bulletEnabled val="1"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr/>
+    </dgm:pt>
+  </dgm:ptLst>
+  <dgm:cxnLst>
+    <dgm:cxn modelId="{4D5D541A-2B93-4624-92B3-D59FA3AC1E73}" srcId="{A80E0E70-3605-43C1-896B-9E0E2DA76989}" destId="{019F7FC0-8C7A-47FC-B340-709D6BB4F28C}" srcOrd="1" destOrd="0" parTransId="{86C45E07-DE6E-4948-B6E8-3578519D54CF}" sibTransId="{5F1AC7EC-5765-409E-B136-EE8AAEF13065}"/>
+    <dgm:cxn modelId="{A2FCB026-170C-4492-8876-DC1D0BCD4EAF}" type="presOf" srcId="{F49C658C-10D3-4771-BEEA-9451B8942588}" destId="{F7A8CD19-F803-4157-B6EC-3C39C3F72FAD}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hProcess9"/>
+    <dgm:cxn modelId="{D8246C2E-8828-46CC-8BD8-ECCE985D1B42}" type="presOf" srcId="{6E31ABEB-3664-4065-A90E-022334D1CA1B}" destId="{F1BA3163-B742-47E9-9399-FD9E172DCCD4}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hProcess9"/>
+    <dgm:cxn modelId="{B02DA946-26C9-467D-BFA2-27203C1A2EB7}" srcId="{07D39319-F6E7-4B32-8B52-F78600763031}" destId="{55F473C3-FE38-4F89-A48A-F8616C607E64}" srcOrd="1" destOrd="0" parTransId="{C143A2A3-4D38-4F3C-AF0A-B70CFA186F8F}" sibTransId="{401A0670-2781-4ECB-BBEA-868183E0129D}"/>
+    <dgm:cxn modelId="{25230855-7956-4E1F-AD79-933BC22CCC31}" type="presOf" srcId="{07D39319-F6E7-4B32-8B52-F78600763031}" destId="{C75E2687-E3E1-4FB6-A473-6B5A0BA5A8EB}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hProcess9"/>
+    <dgm:cxn modelId="{9B3AE875-6892-497B-8A80-12DEB50BE70C}" srcId="{A80E0E70-3605-43C1-896B-9E0E2DA76989}" destId="{D51B010A-3DEB-400F-8603-09D23BDF844C}" srcOrd="0" destOrd="0" parTransId="{656E1BE1-D482-4598-A79D-C5541D65E632}" sibTransId="{189D73AC-6EC1-4E10-A0FE-0AE330FD69C9}"/>
+    <dgm:cxn modelId="{DD3F267D-A547-4261-A8FD-58EDBD31B00A}" type="presOf" srcId="{A80E0E70-3605-43C1-896B-9E0E2DA76989}" destId="{3199F3B8-5EC2-4F94-976C-2EBE9DEB433A}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hProcess9"/>
+    <dgm:cxn modelId="{BA598CB1-815E-4D99-87AC-6D52764CBE92}" srcId="{07D39319-F6E7-4B32-8B52-F78600763031}" destId="{87DA0775-CFC5-4542-A673-22DA53EE1FB3}" srcOrd="0" destOrd="0" parTransId="{A0F696CE-20F0-46F6-8BA1-339843D73582}" sibTransId="{BE2F7E7D-4ED3-45C8-A4D2-2734A70E1720}"/>
+    <dgm:cxn modelId="{A9534EB2-A42A-4119-8193-048B8796EC07}" type="presOf" srcId="{D51B010A-3DEB-400F-8603-09D23BDF844C}" destId="{3199F3B8-5EC2-4F94-976C-2EBE9DEB433A}" srcOrd="0" destOrd="1" presId="urn:microsoft.com/office/officeart/2005/8/layout/hProcess9"/>
+    <dgm:cxn modelId="{BD65F4B5-6C47-4102-998E-0B139484464E}" type="presOf" srcId="{019F7FC0-8C7A-47FC-B340-709D6BB4F28C}" destId="{3199F3B8-5EC2-4F94-976C-2EBE9DEB433A}" srcOrd="0" destOrd="2" presId="urn:microsoft.com/office/officeart/2005/8/layout/hProcess9"/>
+    <dgm:cxn modelId="{9345E2B9-12C8-42C1-980F-4D1E95F22408}" srcId="{F49C658C-10D3-4771-BEEA-9451B8942588}" destId="{6E31ABEB-3664-4065-A90E-022334D1CA1B}" srcOrd="2" destOrd="0" parTransId="{3367770C-714A-4F20-9B4D-629D5F9916B1}" sibTransId="{52DE96E7-F507-40BD-8510-6294B772A5B5}"/>
+    <dgm:cxn modelId="{B2425EBA-6979-4630-8784-B66F479430CF}" type="presOf" srcId="{55F473C3-FE38-4F89-A48A-F8616C607E64}" destId="{C75E2687-E3E1-4FB6-A473-6B5A0BA5A8EB}" srcOrd="0" destOrd="2" presId="urn:microsoft.com/office/officeart/2005/8/layout/hProcess9"/>
+    <dgm:cxn modelId="{1FFE1FC8-FA3A-4625-9B28-E892EDBAB31C}" srcId="{F49C658C-10D3-4771-BEEA-9451B8942588}" destId="{07D39319-F6E7-4B32-8B52-F78600763031}" srcOrd="1" destOrd="0" parTransId="{06B09E15-DAFE-4287-BC51-34DA9409AC51}" sibTransId="{A035C452-63CD-4181-890B-1FF929F042A3}"/>
+    <dgm:cxn modelId="{F548D8CD-99BB-40EF-AC88-99C1FE465551}" type="presOf" srcId="{87DA0775-CFC5-4542-A673-22DA53EE1FB3}" destId="{C75E2687-E3E1-4FB6-A473-6B5A0BA5A8EB}" srcOrd="0" destOrd="1" presId="urn:microsoft.com/office/officeart/2005/8/layout/hProcess9"/>
+    <dgm:cxn modelId="{5A30BAE3-97B7-4F01-80BE-AF1EFD64FEDB}" srcId="{F49C658C-10D3-4771-BEEA-9451B8942588}" destId="{A80E0E70-3605-43C1-896B-9E0E2DA76989}" srcOrd="0" destOrd="0" parTransId="{043BDE8D-8156-41E6-8A4F-E9FA440DDBFD}" sibTransId="{5EA87B87-D2EC-4939-953D-A5B1B33D8508}"/>
+    <dgm:cxn modelId="{D851522E-DBFA-43F9-A4DE-16C753C2A492}" type="presParOf" srcId="{F7A8CD19-F803-4157-B6EC-3C39C3F72FAD}" destId="{02BFDC3E-9A59-43F4-B090-534F9CA78771}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hProcess9"/>
+    <dgm:cxn modelId="{24EECB7E-F17A-44E7-A714-C87184F1CC97}" type="presParOf" srcId="{F7A8CD19-F803-4157-B6EC-3C39C3F72FAD}" destId="{63F0A124-DA13-4157-9743-CDDDBF503FF5}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hProcess9"/>
+    <dgm:cxn modelId="{96E2D987-3887-47E2-8DA2-BBF6BF7091B2}" type="presParOf" srcId="{63F0A124-DA13-4157-9743-CDDDBF503FF5}" destId="{3199F3B8-5EC2-4F94-976C-2EBE9DEB433A}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hProcess9"/>
+    <dgm:cxn modelId="{E0DB5F0D-4777-4281-B226-C6379DFAC09A}" type="presParOf" srcId="{63F0A124-DA13-4157-9743-CDDDBF503FF5}" destId="{5B80FEB3-7CCF-4C21-9372-A1B12C42CC4C}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hProcess9"/>
+    <dgm:cxn modelId="{0829E7DC-EFC6-4A5C-BAAA-CC9A954286B8}" type="presParOf" srcId="{63F0A124-DA13-4157-9743-CDDDBF503FF5}" destId="{C75E2687-E3E1-4FB6-A473-6B5A0BA5A8EB}" srcOrd="2" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hProcess9"/>
+    <dgm:cxn modelId="{ABE9B623-4F16-40D2-8C5F-271B4A56853C}" type="presParOf" srcId="{63F0A124-DA13-4157-9743-CDDDBF503FF5}" destId="{15BEE5DF-1DEF-4917-A925-79DF5FEC74C0}" srcOrd="3" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hProcess9"/>
+    <dgm:cxn modelId="{C9E18F21-2075-496E-A87A-D1253EA5F88C}" type="presParOf" srcId="{63F0A124-DA13-4157-9743-CDDDBF503FF5}" destId="{F1BA3163-B742-47E9-9399-FD9E172DCCD4}" srcOrd="4" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hProcess9"/>
+  </dgm:cxnLst>
+  <dgm:bg/>
+  <dgm:whole/>
+  <dgm:extLst>
+    <a:ext uri="http://schemas.microsoft.com/office/drawing/2008/diagram">
+      <dsp:dataModelExt xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" relId="rId6" minVer="http://schemas.openxmlformats.org/drawingml/2006/diagram"/>
+    </a:ext>
+  </dgm:extLst>
+</dgm:dataModel>
+</file>
+
+<file path=xl/diagrams/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<dsp:drawing xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <dsp:spTree>
+    <dsp:nvGrpSpPr>
+      <dsp:cNvPr id="0" name=""/>
+      <dsp:cNvGrpSpPr/>
+    </dsp:nvGrpSpPr>
+    <dsp:grpSpPr/>
+    <dsp:sp modelId="{02BFDC3E-9A59-43F4-B090-534F9CA78771}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="342899" y="0"/>
+          <a:ext cx="3886200" cy="2743200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:tint val="40000"/>
+            <a:hueOff val="0"/>
+            <a:satOff val="0"/>
+            <a:lumOff val="0"/>
+            <a:alphaOff val="0"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </dsp:style>
+    </dsp:sp>
+    <dsp:sp modelId="{3199F3B8-5EC2-4F94-976C-2EBE9DEB433A}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="154930" y="822960"/>
+          <a:ext cx="1371600" cy="1097280"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:hueOff val="0"/>
+            <a:satOff val="0"/>
+            <a:lumOff val="0"/>
+            <a:alphaOff val="0"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="15875" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="53340" tIns="53340" rIns="53340" bIns="53340" numCol="1" spcCol="1270" anchor="t" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="l" defTabSz="622300">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-IE" sz="1400" kern="1200"/>
+            <a:t>Make Money</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="57150" lvl="1" indent="-57150" algn="l" defTabSz="488950">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="15000"/>
+            </a:spcAft>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-IE" sz="1100" kern="1200"/>
+            <a:t> Work</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="57150" lvl="1" indent="-57150" algn="l" defTabSz="488950">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="15000"/>
+            </a:spcAft>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-IE" sz="1100" kern="1200"/>
+            <a:t>Ask my Mom</a:t>
+          </a:r>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="208495" y="876525"/>
+        <a:ext cx="1264470" cy="990150"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{C75E2687-E3E1-4FB6-A473-6B5A0BA5A8EB}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="1600199" y="822960"/>
+          <a:ext cx="1371600" cy="1097280"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:hueOff val="0"/>
+            <a:satOff val="0"/>
+            <a:lumOff val="0"/>
+            <a:alphaOff val="0"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="15875" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="53340" tIns="53340" rIns="53340" bIns="53340" numCol="1" spcCol="1270" anchor="t" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="l" defTabSz="622300">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-IE" sz="1400" kern="1200"/>
+            <a:t>Spend Money</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="57150" lvl="1" indent="-57150" algn="l" defTabSz="488950">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="15000"/>
+            </a:spcAft>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-IE" sz="1100" kern="1200"/>
+            <a:t>Monthly Fixed Expenses</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="57150" lvl="1" indent="-57150" algn="l" defTabSz="488950">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="15000"/>
+            </a:spcAft>
+            <a:buChar char="•"/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-IE" sz="1100" kern="1200"/>
+            <a:t>Monthly Variable Expenses</a:t>
+          </a:r>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="1653764" y="876525"/>
+        <a:ext cx="1264470" cy="990150"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{F1BA3163-B742-47E9-9399-FD9E172DCCD4}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="3045469" y="822960"/>
+          <a:ext cx="1371600" cy="1097280"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:hueOff val="0"/>
+            <a:satOff val="0"/>
+            <a:lumOff val="0"/>
+            <a:alphaOff val="0"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="15875" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="53340" tIns="53340" rIns="53340" bIns="53340" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="622300">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-IE" sz="1400" kern="1200"/>
+            <a:t>Track Money</a:t>
+          </a:r>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="3099034" y="876525"/>
+        <a:ext cx="1264470" cy="990150"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+  </dsp:spTree>
+</dsp:drawing>
+</file>
+
+<file path=xl/diagrams/layout1.xml><?xml version="1.0" encoding="utf-8"?>
+<dgm:layoutDef xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uniqueId="urn:microsoft.com/office/officeart/2005/8/layout/hProcess9">
+  <dgm:title val=""/>
+  <dgm:desc val=""/>
+  <dgm:catLst>
+    <dgm:cat type="process" pri="5000"/>
+    <dgm:cat type="convert" pri="13000"/>
+  </dgm:catLst>
+  <dgm:sampData useDef="1">
+    <dgm:dataModel>
+      <dgm:ptLst/>
+      <dgm:bg/>
+      <dgm:whole/>
+    </dgm:dataModel>
+  </dgm:sampData>
+  <dgm:styleData>
+    <dgm:dataModel>
+      <dgm:ptLst>
+        <dgm:pt modelId="0" type="doc"/>
+        <dgm:pt modelId="1"/>
+        <dgm:pt modelId="2"/>
+      </dgm:ptLst>
+      <dgm:cxnLst>
+        <dgm:cxn modelId="3" srcId="0" destId="1" srcOrd="0" destOrd="0"/>
+        <dgm:cxn modelId="4" srcId="0" destId="2" srcOrd="1" destOrd="0"/>
+      </dgm:cxnLst>
+      <dgm:bg/>
+      <dgm:whole/>
+    </dgm:dataModel>
+  </dgm:styleData>
+  <dgm:clrData>
+    <dgm:dataModel>
+      <dgm:ptLst>
+        <dgm:pt modelId="0" type="doc"/>
+        <dgm:pt modelId="1"/>
+        <dgm:pt modelId="2"/>
+        <dgm:pt modelId="3"/>
+        <dgm:pt modelId="4"/>
+      </dgm:ptLst>
+      <dgm:cxnLst>
+        <dgm:cxn modelId="5" srcId="0" destId="1" srcOrd="0" destOrd="0"/>
+        <dgm:cxn modelId="6" srcId="0" destId="2" srcOrd="1" destOrd="0"/>
+        <dgm:cxn modelId="7" srcId="0" destId="3" srcOrd="2" destOrd="0"/>
+        <dgm:cxn modelId="8" srcId="0" destId="4" srcOrd="3" destOrd="0"/>
+      </dgm:cxnLst>
+      <dgm:bg/>
+      <dgm:whole/>
+    </dgm:dataModel>
+  </dgm:clrData>
+  <dgm:layoutNode name="CompostProcess">
+    <dgm:varLst>
+      <dgm:dir/>
+      <dgm:resizeHandles val="exact"/>
+    </dgm:varLst>
+    <dgm:alg type="composite">
+      <dgm:param type="horzAlign" val="ctr"/>
+      <dgm:param type="vertAlign" val="mid"/>
+    </dgm:alg>
+    <dgm:shape xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:blip="">
+      <dgm:adjLst/>
+    </dgm:shape>
+    <dgm:presOf/>
+    <dgm:constrLst>
+      <dgm:constr type="w" for="ch" forName="arrow" refType="w" fact="0.85"/>
+      <dgm:constr type="h" for="ch" forName="arrow" refType="h"/>
+      <dgm:constr type="ctrX" for="ch" forName="arrow" refType="w" fact="0.5"/>
+      <dgm:constr type="ctrY" for="ch" forName="arrow" refType="h" fact="0.5"/>
+      <dgm:constr type="w" for="ch" forName="linearProcess" refType="w"/>
+      <dgm:constr type="h" for="ch" forName="linearProcess" refType="h" fact="0.4"/>
+      <dgm:constr type="ctrX" for="ch" forName="linearProcess" refType="w" fact="0.5"/>
+      <dgm:constr type="ctrY" for="ch" forName="linearProcess" refType="h" fact="0.5"/>
+    </dgm:constrLst>
+    <dgm:ruleLst/>
+    <dgm:layoutNode name="arrow" styleLbl="bgShp">
+      <dgm:alg type="sp"/>
+      <dgm:choose name="Name0">
+        <dgm:if name="Name1" func="var" arg="dir" op="equ" val="norm">
+          <dgm:shape xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" type="rightArrow" r:blip="">
+            <dgm:adjLst/>
+          </dgm:shape>
+        </dgm:if>
+        <dgm:else name="Name2">
+          <dgm:shape xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" type="leftArrow" r:blip="">
+            <dgm:adjLst/>
+          </dgm:shape>
+        </dgm:else>
+      </dgm:choose>
+      <dgm:presOf/>
+      <dgm:constrLst/>
+      <dgm:ruleLst/>
+    </dgm:layoutNode>
+    <dgm:layoutNode name="linearProcess">
+      <dgm:choose name="Name3">
+        <dgm:if name="Name4" func="var" arg="dir" op="equ" val="norm">
+          <dgm:alg type="lin"/>
+        </dgm:if>
+        <dgm:else name="Name5">
+          <dgm:alg type="lin">
+            <dgm:param type="linDir" val="fromR"/>
+          </dgm:alg>
+        </dgm:else>
+      </dgm:choose>
+      <dgm:shape xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:blip="">
+        <dgm:adjLst/>
+      </dgm:shape>
+      <dgm:presOf/>
+      <dgm:constrLst>
+        <dgm:constr type="userA" for="ch" ptType="node" refType="w"/>
+        <dgm:constr type="h" for="ch" ptType="node" refType="h"/>
+        <dgm:constr type="w" for="ch" ptType="node" op="equ"/>
+        <dgm:constr type="w" for="ch" forName="sibTrans" refType="w" fact="0.05"/>
+        <dgm:constr type="primFontSz" for="ch" ptType="node" op="equ" val="65"/>
+      </dgm:constrLst>
+      <dgm:ruleLst/>
+      <dgm:forEach name="Name6" axis="ch" ptType="node">
+        <dgm:layoutNode name="textNode" styleLbl="node1">
+          <dgm:varLst>
+            <dgm:bulletEnabled val="1"/>
+          </dgm:varLst>
+          <dgm:alg type="tx"/>
+          <dgm:shape xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" type="roundRect" r:blip="">
+            <dgm:adjLst/>
+          </dgm:shape>
+          <dgm:presOf axis="desOrSelf" ptType="node"/>
+          <dgm:constrLst>
+            <dgm:constr type="userA"/>
+            <dgm:constr type="w" refType="userA" fact="0.3"/>
+            <dgm:constr type="tMarg" refType="primFontSz" fact="0.3"/>
+            <dgm:constr type="bMarg" refType="primFontSz" fact="0.3"/>
+            <dgm:constr type="lMarg" refType="primFontSz" fact="0.3"/>
+            <dgm:constr type="rMarg" refType="primFontSz" fact="0.3"/>
+          </dgm:constrLst>
+          <dgm:ruleLst>
+            <dgm:rule type="w" val="NaN" fact="1" max="NaN"/>
+            <dgm:rule type="primFontSz" val="5" fact="NaN" max="NaN"/>
+          </dgm:ruleLst>
+        </dgm:layoutNode>
+        <dgm:forEach name="Name7" axis="followSib" ptType="sibTrans" cnt="1">
+          <dgm:layoutNode name="sibTrans">
+            <dgm:alg type="sp"/>
+            <dgm:shape xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:blip="">
+              <dgm:adjLst/>
+            </dgm:shape>
+            <dgm:presOf/>
+            <dgm:constrLst/>
+            <dgm:ruleLst/>
+          </dgm:layoutNode>
+        </dgm:forEach>
+      </dgm:forEach>
+    </dgm:layoutNode>
+  </dgm:layoutNode>
+</dgm:layoutDef>
+</file>
+
+<file path=xl/diagrams/quickStyle1.xml><?xml version="1.0" encoding="utf-8"?>
+<dgm:styleDef xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uniqueId="urn:microsoft.com/office/officeart/2005/8/quickstyle/simple1">
+  <dgm:title val=""/>
+  <dgm:desc val=""/>
+  <dgm:catLst>
+    <dgm:cat type="simple" pri="10100"/>
+  </dgm:catLst>
+  <dgm:scene3d>
+    <a:camera prst="orthographicFront"/>
+    <a:lightRig rig="threePt" dir="t"/>
+  </dgm:scene3d>
+  <dgm:styleLbl name="node0">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="lnNode1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="vennNode1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="tx1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="alignNode1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="node1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="node2">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="node3">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="node4">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgImgPlace1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="alignImgPlace1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="bgImgPlace1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="sibTrans2D1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgSibTrans2D1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="bgSibTrans2D1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="sibTrans1D1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="callout">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="asst0">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="asst1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="asst2">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="asst3">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="asst4">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans2D1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans2D2">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans2D3">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans2D4">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans1D1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans1D2">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans1D3">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans1D4">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgAcc1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="conFgAcc1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="alignAcc1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="trAlignAcc1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="bgAcc1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="solidFgAcc1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="solidAlignAcc1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="solidBgAcc1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgAccFollowNode1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="alignAccFollowNode1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="bgAccFollowNode1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgAcc0">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgAcc2">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgAcc3">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgAcc4">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="bgShp">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="dkBgShp">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="trBgShp">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgShp">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="revTx">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+</dgm:styleDef>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>198120</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>685800</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>173708</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>708659</xdr:colOff>
+      <xdr:colOff>289559</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>569943</xdr:rowOff>
     </xdr:to>
@@ -317,7 +5725,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4373880" y="173708"/>
+          <a:off x="3954780" y="173708"/>
           <a:ext cx="510539" cy="571495"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -330,15 +5738,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>220980</xdr:colOff>
+      <xdr:colOff>601980</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>731519</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>205739</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>579115</xdr:rowOff>
+      <xdr:rowOff>571495</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -361,7 +5769,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8023860" y="182880"/>
+          <a:off x="8404860" y="175260"/>
           <a:ext cx="510539" cy="571495"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -371,6 +5779,1048 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>60960</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>205740</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>502920</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Arrow: Left 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4276DB8A-B178-18F4-DCA3-A3419F6EE32E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13434060" y="1158240"/>
+          <a:ext cx="441960" cy="251460"/>
+        </a:xfrm>
+        <a:prstGeom prst="leftArrow">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 19697"/>
+            <a:gd name="adj2" fmla="val 53030"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="C00000"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FFFF00"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IE" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>838200</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>594360</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>533400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="Lightning Bolt 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E73822E2-FA79-411B-B3D7-4B6F622336AC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3200400" y="281940"/>
+          <a:ext cx="662940" cy="426720"/>
+        </a:xfrm>
+        <a:prstGeom prst="lightningBolt">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IE" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>182880</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>845820</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>518160</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Lightning Bolt 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00C86D77-EFD2-4592-9A07-45A407D63AD2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8892540" y="266700"/>
+          <a:ext cx="662940" cy="426720"/>
+        </a:xfrm>
+        <a:prstGeom prst="lightningBolt">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF00"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IE" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>274320</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>289560</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>708660</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>518160</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="Cube 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0F37ED7-9860-0631-3115-F87D7118A674}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2636520" y="464820"/>
+          <a:ext cx="434340" cy="228600"/>
+        </a:xfrm>
+        <a:prstGeom prst="cube">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="C00000"/>
+        </a:solidFill>
+        <a:scene3d>
+          <a:camera prst="perspectiveAbove"/>
+          <a:lightRig rig="threePt" dir="t"/>
+        </a:scene3d>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:endParaRPr lang="en-IE" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>83820</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>297180</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>518160</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>525780</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="Cube 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E67CE016-2480-43FB-8EFE-E4469A8548F0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9700260" y="472440"/>
+          <a:ext cx="434340" cy="228600"/>
+        </a:xfrm>
+        <a:prstGeom prst="cube">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="C00000"/>
+        </a:solidFill>
+        <a:scene3d>
+          <a:camera prst="perspectiveAbove"/>
+          <a:lightRig rig="threePt" dir="t"/>
+        </a:scene3d>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:endParaRPr lang="en-IE" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>601980</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>289560</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>129540</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>518160</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="Cube 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36FA1FDC-4902-4190-B90C-7DF171246B99}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10218420" y="464820"/>
+          <a:ext cx="434340" cy="228600"/>
+        </a:xfrm>
+        <a:prstGeom prst="cube">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="C00000"/>
+        </a:solidFill>
+        <a:scene3d>
+          <a:camera prst="perspectiveAbove"/>
+          <a:lightRig rig="threePt" dir="t"/>
+        </a:scene3d>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:endParaRPr lang="en-IE" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>632460</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>297180</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>160020</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>525780</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="Cube 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{849CEEB9-6D1A-4DED-B801-E8B125350F2A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2087880" y="472440"/>
+          <a:ext cx="434340" cy="228600"/>
+        </a:xfrm>
+        <a:prstGeom prst="cube">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="C00000"/>
+        </a:solidFill>
+        <a:scene3d>
+          <a:camera prst="perspectiveAbove"/>
+          <a:lightRig rig="threePt" dir="t"/>
+        </a:scene3d>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:endParaRPr lang="en-IE" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>106680</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>304800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>541020</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>533400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="Cube 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8567FD9-38D0-4A6B-BEE4-98E16626FF78}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1562100" y="480060"/>
+          <a:ext cx="434340" cy="228600"/>
+        </a:xfrm>
+        <a:prstGeom prst="cube">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="C00000"/>
+        </a:solidFill>
+        <a:scene3d>
+          <a:camera prst="perspectiveAbove"/>
+          <a:lightRig rig="threePt" dir="t"/>
+        </a:scene3d>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:endParaRPr lang="en-IE" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>213360</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>281940</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>510540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="Cube 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{341DB6C5-87A7-48D0-8F05-1A6E011AD71D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10736580" y="457200"/>
+          <a:ext cx="434340" cy="228600"/>
+        </a:xfrm>
+        <a:prstGeom prst="cube">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="C00000"/>
+        </a:solidFill>
+        <a:scene3d>
+          <a:camera prst="perspectiveAbove"/>
+          <a:lightRig rig="threePt" dir="t"/>
+        </a:scene3d>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:endParaRPr lang="en-IE" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>731520</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>289560</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>259080</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>518160</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="Cube 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{052AF7E7-5649-48F8-A097-DB79090044B7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11254740" y="464820"/>
+          <a:ext cx="434340" cy="228600"/>
+        </a:xfrm>
+        <a:prstGeom prst="cube">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="C00000"/>
+        </a:solidFill>
+        <a:scene3d>
+          <a:camera prst="perspectiveAbove"/>
+          <a:lightRig rig="threePt" dir="t"/>
+        </a:scene3d>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:endParaRPr lang="en-IE" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>320040</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>281940</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>754380</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>510540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="Cube 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E50ED169-E376-40D9-82DC-9E0589AA6ABA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11750040" y="457200"/>
+          <a:ext cx="434340" cy="228600"/>
+        </a:xfrm>
+        <a:prstGeom prst="cube">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="C00000"/>
+        </a:solidFill>
+        <a:scene3d>
+          <a:camera prst="perspectiveAbove"/>
+          <a:lightRig rig="threePt" dir="t"/>
+        </a:scene3d>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:endParaRPr lang="en-IE" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>304800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>533400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="Cube 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{520C349B-76CB-4DE3-8B70-CC477A5C1A64}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1028700" y="480060"/>
+          <a:ext cx="434340" cy="228600"/>
+        </a:xfrm>
+        <a:prstGeom prst="cube">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="C00000"/>
+        </a:solidFill>
+        <a:scene3d>
+          <a:camera prst="perspectiveAbove"/>
+          <a:lightRig rig="threePt" dir="t"/>
+        </a:scene3d>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:endParaRPr lang="en-IE" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>45720</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>312420</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>480060</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>541020</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="Cube 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B0E9642-0286-4F0D-A8BF-AF578CD8CED7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="502920" y="487680"/>
+          <a:ext cx="434340" cy="228600"/>
+        </a:xfrm>
+        <a:prstGeom prst="cube">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="C00000"/>
+        </a:solidFill>
+        <a:scene3d>
+          <a:camera prst="perspectiveAbove"/>
+          <a:lightRig rig="threePt" dir="t"/>
+        </a:scene3d>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:endParaRPr lang="en-IE" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>278130</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>674370</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="19" name="Diagram 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB0B663E-6451-2111-8D35-446E052D1188}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/diagram">
+          <dgm:relIds xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:dm="rId2" r:lo="rId3" r:qs="rId4" r:cs="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>331470</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>198120</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>556260</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="23" name="Chart 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{84360FC0-6D8A-92D5-3168-3C5DBB8AECB0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="0" y="0"/>
+    <xdr:ext cx="9289143" cy="6068786"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{25882FF3-DCE9-55CB-8AC3-E818AAEFDAF6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks noGrp="1"/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
 </xdr:wsDr>
 </file>
 
@@ -643,701 +7093,701 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:17" ht="47.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="8"/>
-      <c r="C2" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B3" s="8"/>
+      <c r="B3" s="3"/>
     </row>
     <row r="4" spans="2:17" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="8"/>
-      <c r="C4" s="11" t="s">
+      <c r="B4" s="3"/>
+      <c r="C4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="6">
+        <v>45658</v>
+      </c>
+      <c r="E4" s="6">
+        <v>45689</v>
+      </c>
+      <c r="F4" s="6">
+        <v>45717</v>
+      </c>
+      <c r="G4" s="6">
+        <v>45748</v>
+      </c>
+      <c r="H4" s="6">
+        <v>45778</v>
+      </c>
+      <c r="I4" s="6">
+        <v>45809</v>
+      </c>
+      <c r="J4" s="6">
+        <v>45839</v>
+      </c>
+      <c r="K4" s="6">
+        <v>45870</v>
+      </c>
+      <c r="L4" s="6">
+        <v>45901</v>
+      </c>
+      <c r="M4" s="6">
+        <v>45931</v>
+      </c>
+      <c r="N4" s="6">
+        <v>45962</v>
+      </c>
+      <c r="O4" s="6">
+        <v>45992</v>
+      </c>
+      <c r="P4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q4" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="2:17" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="3"/>
+      <c r="C5" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="12">
-        <v>45658</v>
-      </c>
-      <c r="E4" s="12">
-        <v>45689</v>
-      </c>
-      <c r="F4" s="12">
-        <v>45717</v>
-      </c>
-      <c r="G4" s="12">
-        <v>45748</v>
-      </c>
-      <c r="H4" s="12">
-        <v>45778</v>
-      </c>
-      <c r="I4" s="12">
-        <v>45809</v>
-      </c>
-      <c r="J4" s="12">
-        <v>45839</v>
-      </c>
-      <c r="K4" s="12">
-        <v>45870</v>
-      </c>
-      <c r="L4" s="12">
-        <v>45901</v>
-      </c>
-      <c r="M4" s="12">
-        <v>45931</v>
-      </c>
-      <c r="N4" s="12">
-        <v>45962</v>
-      </c>
-      <c r="O4" s="12">
-        <v>45992</v>
-      </c>
-      <c r="P4" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q4" s="11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="2:17" ht="14.4" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="8"/>
-      <c r="C5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="1">
+      <c r="D5" s="9">
         <v>725</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="9">
         <v>725</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="9">
         <v>725</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" s="9">
         <v>725</v>
       </c>
-      <c r="H5" s="1">
+      <c r="H5" s="9">
         <v>725</v>
       </c>
-      <c r="I5" s="1">
+      <c r="I5" s="9">
         <v>725</v>
       </c>
-      <c r="J5" s="1">
+      <c r="J5" s="9">
         <v>725</v>
       </c>
-      <c r="K5" s="1">
+      <c r="K5" s="9">
         <v>725</v>
       </c>
-      <c r="L5" s="1">
+      <c r="L5" s="9">
         <v>725</v>
       </c>
-      <c r="M5" s="1">
+      <c r="M5" s="9">
         <v>725</v>
       </c>
-      <c r="N5" s="1">
+      <c r="N5" s="9">
         <v>725</v>
       </c>
-      <c r="O5" s="1">
+      <c r="O5" s="9">
         <v>725</v>
       </c>
-      <c r="P5">
+      <c r="P5" s="8">
         <f t="shared" ref="P5:P11" si="0">SUM(D5:O5)</f>
         <v>8700</v>
       </c>
-      <c r="Q5" s="9">
+      <c r="Q5" s="10">
         <f t="shared" ref="Q5:Q10" si="1">P5/$P$11</f>
         <v>0.52858618385078071</v>
       </c>
     </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B6" s="8"/>
-      <c r="C6" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="6">
+    <row r="6" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B6" s="3"/>
+      <c r="C6" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="11">
         <v>20</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="11">
         <v>20</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="11">
         <v>20</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="11">
         <v>20</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="11">
         <v>20</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="11">
         <v>20</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="11">
         <v>20</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="11">
         <v>20</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="11">
         <v>20</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="11">
         <v>20</v>
       </c>
-      <c r="N6" s="6">
+      <c r="N6" s="11">
         <v>20</v>
       </c>
-      <c r="O6" s="6">
+      <c r="O6" s="11">
         <v>20</v>
       </c>
-      <c r="P6">
+      <c r="P6" s="8">
         <f t="shared" si="0"/>
         <v>240</v>
       </c>
-      <c r="Q6" s="9">
+      <c r="Q6" s="10">
         <f t="shared" si="1"/>
         <v>1.4581687830366365E-2</v>
       </c>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B7" s="8"/>
-      <c r="C7" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="6">
+    <row r="7" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B7" s="3"/>
+      <c r="C7" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="11">
         <v>400</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="11">
         <v>400</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="11">
         <v>400</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="11">
         <v>400</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="11">
         <v>10</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="11">
         <v>5</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="11">
         <v>17</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="11">
         <v>8</v>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="11">
         <v>10</v>
       </c>
-      <c r="M7" s="6">
+      <c r="M7" s="11">
         <v>15</v>
       </c>
-      <c r="N7" s="6">
+      <c r="N7" s="11">
         <v>25</v>
       </c>
-      <c r="O7" s="6">
+      <c r="O7" s="11">
         <v>35</v>
       </c>
-      <c r="P7">
+      <c r="P7" s="8">
         <f t="shared" si="0"/>
         <v>1725</v>
       </c>
-      <c r="Q7" s="9">
+      <c r="Q7" s="10">
         <f t="shared" si="1"/>
         <v>0.10480588128075825</v>
       </c>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B8" s="8"/>
-      <c r="C8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="6">
+    <row r="8" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B8" s="3"/>
+      <c r="C8" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="11">
         <v>40</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="11">
         <v>40</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="11">
         <v>40</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="11">
         <v>40</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="11">
         <v>40</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="11">
         <v>40</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="11">
         <v>40</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="11">
         <v>40</v>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="11">
         <v>40</v>
       </c>
-      <c r="M8" s="6">
+      <c r="M8" s="11">
         <v>40</v>
       </c>
-      <c r="N8" s="6">
+      <c r="N8" s="11">
         <v>40</v>
       </c>
-      <c r="O8" s="6">
+      <c r="O8" s="11">
         <v>40</v>
       </c>
-      <c r="P8">
+      <c r="P8" s="8">
         <f t="shared" si="0"/>
         <v>480</v>
       </c>
-      <c r="Q8" s="9">
+      <c r="Q8" s="10">
         <f t="shared" si="1"/>
         <v>2.9163375660732731E-2</v>
       </c>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B9" s="8"/>
-      <c r="C9" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="6">
+    <row r="9" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B9" s="3"/>
+      <c r="C9" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="11">
         <v>400</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="11">
         <v>450</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="11">
         <v>400</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="11">
         <v>400</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="11">
         <v>450</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="11">
         <v>400</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="11">
         <v>450</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="11">
         <v>350</v>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="11">
         <v>400</v>
       </c>
-      <c r="M9" s="6">
+      <c r="M9" s="11">
         <v>450</v>
       </c>
-      <c r="N9" s="6">
+      <c r="N9" s="11">
         <v>350</v>
       </c>
-      <c r="O9" s="6">
+      <c r="O9" s="11">
         <v>450</v>
       </c>
-      <c r="P9">
+      <c r="P9" s="8">
         <f t="shared" si="0"/>
         <v>4950</v>
       </c>
-      <c r="Q9" s="9">
+      <c r="Q9" s="10">
         <f t="shared" si="1"/>
         <v>0.30074731150130629</v>
       </c>
     </row>
-    <row r="10" spans="2:17" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="8"/>
-      <c r="C10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="7">
+    <row r="10" spans="2:17" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="3"/>
+      <c r="C10" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="12">
         <v>15</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="12">
         <v>20</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="12">
         <v>15</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="12">
         <v>25</v>
       </c>
-      <c r="H10" s="7">
+      <c r="H10" s="12">
         <v>35</v>
       </c>
-      <c r="I10" s="7">
+      <c r="I10" s="12">
         <v>45</v>
       </c>
-      <c r="J10" s="7">
+      <c r="J10" s="12">
         <v>25</v>
       </c>
-      <c r="K10" s="7">
+      <c r="K10" s="12">
         <v>35</v>
       </c>
-      <c r="L10" s="7">
+      <c r="L10" s="12">
         <v>25</v>
       </c>
-      <c r="M10" s="7">
+      <c r="M10" s="12">
         <v>14</v>
       </c>
-      <c r="N10" s="7">
+      <c r="N10" s="12">
         <v>35</v>
       </c>
-      <c r="O10" s="7">
+      <c r="O10" s="12">
         <v>75</v>
       </c>
-      <c r="P10">
+      <c r="P10" s="8">
         <f t="shared" si="0"/>
         <v>364</v>
       </c>
-      <c r="Q10" s="9">
+      <c r="Q10" s="10">
         <f t="shared" si="1"/>
         <v>2.2115559876055655E-2</v>
       </c>
     </row>
-    <row r="11" spans="2:17" ht="14.4" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="8"/>
-      <c r="C11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="5">
+    <row r="11" spans="2:17" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="3"/>
+      <c r="C11" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="13">
         <f t="shared" ref="D11:O11" si="2">SUM(D5:D10)</f>
         <v>1600</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="13">
         <f t="shared" si="2"/>
         <v>1655</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="13">
         <f t="shared" si="2"/>
         <v>1600</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G11" s="13">
         <f t="shared" si="2"/>
         <v>1610</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11" s="13">
         <f t="shared" si="2"/>
         <v>1280</v>
       </c>
-      <c r="I11" s="5">
+      <c r="I11" s="13">
         <f t="shared" si="2"/>
         <v>1235</v>
       </c>
-      <c r="J11" s="5">
+      <c r="J11" s="13">
         <f t="shared" si="2"/>
         <v>1277</v>
       </c>
-      <c r="K11" s="5">
+      <c r="K11" s="13">
         <f t="shared" si="2"/>
         <v>1178</v>
       </c>
-      <c r="L11" s="5">
+      <c r="L11" s="13">
         <f t="shared" si="2"/>
         <v>1220</v>
       </c>
-      <c r="M11" s="5">
+      <c r="M11" s="13">
         <f t="shared" si="2"/>
         <v>1264</v>
       </c>
-      <c r="N11" s="5">
+      <c r="N11" s="13">
         <f t="shared" si="2"/>
         <v>1195</v>
       </c>
-      <c r="O11" s="5">
+      <c r="O11" s="13">
         <f t="shared" si="2"/>
         <v>1345</v>
       </c>
-      <c r="P11">
+      <c r="P11" s="8">
         <f t="shared" si="0"/>
         <v>16459</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="Q11" s="14">
         <f>SUM(Q5:Q10)</f>
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B12" s="8"/>
+      <c r="B12" s="3"/>
     </row>
     <row r="13" spans="2:17" ht="18" x14ac:dyDescent="0.35">
-      <c r="B13" s="8"/>
-      <c r="C13" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13">
+      <c r="B13" s="3"/>
+      <c r="C13" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="8">
         <f t="shared" ref="D13:O13" si="3">MIN(D5:D10)</f>
         <v>15</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="8">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="8">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="8">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="8">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="8">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="8">
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="8">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="L13">
+      <c r="L13" s="8">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="M13">
+      <c r="M13" s="8">
         <f t="shared" si="3"/>
         <v>14</v>
       </c>
-      <c r="N13">
+      <c r="N13" s="8">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="O13">
+      <c r="O13" s="8">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B14" s="8"/>
-      <c r="C14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14">
+    <row r="14" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B14" s="3"/>
+      <c r="C14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="8">
         <f t="shared" ref="D14:O14" si="4">MAX(D5:D10)</f>
         <v>725</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="8">
         <f t="shared" si="4"/>
         <v>725</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="8">
         <f t="shared" si="4"/>
         <v>725</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="8">
         <f t="shared" si="4"/>
         <v>725</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="8">
         <f t="shared" si="4"/>
         <v>725</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="8">
         <f t="shared" si="4"/>
         <v>725</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="8">
         <f t="shared" si="4"/>
         <v>725</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="8">
         <f t="shared" si="4"/>
         <v>725</v>
       </c>
-      <c r="L14">
+      <c r="L14" s="8">
         <f t="shared" si="4"/>
         <v>725</v>
       </c>
-      <c r="M14">
+      <c r="M14" s="8">
         <f t="shared" si="4"/>
         <v>725</v>
       </c>
-      <c r="N14">
+      <c r="N14" s="8">
         <f t="shared" si="4"/>
         <v>725</v>
       </c>
-      <c r="O14">
+      <c r="O14" s="8">
         <f t="shared" si="4"/>
         <v>725</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B15" s="8"/>
-      <c r="C15" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15">
+    <row r="15" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B15" s="3"/>
+      <c r="C15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="8">
         <f t="shared" ref="D15:O15" si="5">AVERAGE(D5:D10)</f>
         <v>266.66666666666669</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="8">
         <f t="shared" si="5"/>
         <v>275.83333333333331</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="8">
         <f t="shared" si="5"/>
         <v>266.66666666666669</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="8">
         <f t="shared" si="5"/>
         <v>268.33333333333331</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="8">
         <f t="shared" si="5"/>
         <v>213.33333333333334</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="8">
         <f t="shared" si="5"/>
         <v>205.83333333333334</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="8">
         <f t="shared" si="5"/>
         <v>212.83333333333334</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="8">
         <f t="shared" si="5"/>
         <v>196.33333333333334</v>
       </c>
-      <c r="L15">
+      <c r="L15" s="8">
         <f t="shared" si="5"/>
         <v>203.33333333333334</v>
       </c>
-      <c r="M15">
+      <c r="M15" s="8">
         <f t="shared" si="5"/>
         <v>210.66666666666666</v>
       </c>
-      <c r="N15">
+      <c r="N15" s="8">
         <f t="shared" si="5"/>
         <v>199.16666666666666</v>
       </c>
-      <c r="O15">
+      <c r="O15" s="8">
         <f t="shared" si="5"/>
         <v>224.16666666666666</v>
       </c>
     </row>
     <row r="16" spans="2:17" ht="18" x14ac:dyDescent="0.35">
-      <c r="B16" s="8"/>
-      <c r="C16" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16">
+      <c r="B16" s="3"/>
+      <c r="C16" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="8">
         <f t="shared" ref="D16:O16" si="6">COUNT(D5:D10)</f>
         <v>6</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="8">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="8">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="8">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="8">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="8">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="8">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="8">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="L16">
+      <c r="L16" s="8">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="M16">
+      <c r="M16" s="8">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="N16">
+      <c r="N16" s="8">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="O16">
+      <c r="O16" s="8">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
     </row>
     <row r="18" spans="4:5" ht="16.2" x14ac:dyDescent="0.3">
-      <c r="D18" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E18" s="1">
+      <c r="D18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="9">
         <v>100</v>
       </c>
     </row>
     <row r="19" spans="4:5" ht="16.2" x14ac:dyDescent="0.3">
-      <c r="D19" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E19" s="1">
+      <c r="D19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="9">
         <v>150</v>
       </c>
     </row>
     <row r="20" spans="4:5" ht="16.2" x14ac:dyDescent="0.3">
-      <c r="D20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E20" s="1">
+      <c r="D20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="9">
         <v>55</v>
       </c>
     </row>
     <row r="21" spans="4:5" ht="16.2" x14ac:dyDescent="0.3">
-      <c r="D21" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E21" s="1">
+      <c r="D21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="9">
         <f>SUM(E18:E20)</f>
         <v>305</v>
       </c>
     </row>
     <row r="22" spans="4:5" ht="16.2" x14ac:dyDescent="0.3">
-      <c r="D22" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E22" s="2">
+      <c r="D22" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" s="14">
         <v>0.08</v>
       </c>
     </row>
     <row r="23" spans="4:5" ht="16.2" x14ac:dyDescent="0.3">
-      <c r="D23" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E23" s="1">
+      <c r="D23" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23" s="9">
         <f>E21*(E22+1)</f>
         <v>329.40000000000003</v>
       </c>

--- a/Udemy Excel 101.xlsx
+++ b/Udemy Excel 101.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8EF12D157D92B731/Documents/GitHub/Robert-Rookie-project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="321" documentId="8_{8761CF19-0046-4715-B8FB-9230E793B6F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B7C5391-5B0E-4154-882A-F0A08D3AC642}"/>
+  <xr:revisionPtr revIDLastSave="331" documentId="8_{8761CF19-0046-4715-B8FB-9230E793B6F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E9612EA-F344-47FB-8173-CB101B809232}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F602598-B120-46E6-997C-287E091787E5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{9F602598-B120-46E6-997C-287E091787E5}"/>
   </bookViews>
   <sheets>
     <sheet name="Budget " sheetId="7" r:id="rId1"/>
@@ -251,9 +251,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="4"/>
     <xf numFmtId="164" fontId="5" fillId="4" borderId="3" xfId="4" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="3" applyFont="1"/>
@@ -261,6 +258,9 @@
     <xf numFmtId="43" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -4161,8 +4161,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="342899" y="0"/>
-          <a:ext cx="3886200" cy="2743200"/>
+          <a:off x="651918" y="0"/>
+          <a:ext cx="7388406" cy="6384471"/>
         </a:xfrm>
         <a:prstGeom prst="rightArrow">
           <a:avLst/>
@@ -4201,8 +4201,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="154930" y="822960"/>
-          <a:ext cx="1371600" cy="1097280"/>
+          <a:off x="244257" y="1915341"/>
+          <a:ext cx="2607672" cy="2553788"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -4243,12 +4243,12 @@
         </a:fontRef>
       </dsp:style>
       <dsp:txBody>
-        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="53340" tIns="53340" rIns="53340" bIns="53340" numCol="1" spcCol="1270" anchor="t" anchorCtr="0">
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="114300" tIns="114300" rIns="114300" bIns="114300" numCol="1" spcCol="1270" anchor="t" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="l" defTabSz="622300">
+          <a:pPr marL="0" lvl="0" indent="0" algn="l" defTabSz="1333500">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -4261,12 +4261,12 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-IE" sz="1400" kern="1200"/>
+            <a:rPr lang="en-IE" sz="3000" kern="1200"/>
             <a:t>Make Money</a:t>
           </a:r>
         </a:p>
         <a:p>
-          <a:pPr marL="57150" lvl="1" indent="-57150" algn="l" defTabSz="488950">
+          <a:pPr marL="228600" lvl="1" indent="-228600" algn="l" defTabSz="1022350">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -4279,12 +4279,12 @@
             <a:buChar char="•"/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-IE" sz="1100" kern="1200"/>
+            <a:rPr lang="en-IE" sz="2300" kern="1200"/>
             <a:t> Work</a:t>
           </a:r>
         </a:p>
         <a:p>
-          <a:pPr marL="57150" lvl="1" indent="-57150" algn="l" defTabSz="488950">
+          <a:pPr marL="228600" lvl="1" indent="-228600" algn="l" defTabSz="1022350">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -4297,14 +4297,14 @@
             <a:buChar char="•"/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-IE" sz="1100" kern="1200"/>
+            <a:rPr lang="en-IE" sz="2300" kern="1200"/>
             <a:t>Ask my Mom</a:t>
           </a:r>
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="208495" y="876525"/>
-        <a:ext cx="1264470" cy="990150"/>
+        <a:off x="368923" y="2040007"/>
+        <a:ext cx="2358340" cy="2304456"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{C75E2687-E3E1-4FB6-A473-6B5A0BA5A8EB}">
@@ -4314,8 +4314,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="1600199" y="822960"/>
-          <a:ext cx="1371600" cy="1097280"/>
+          <a:off x="3042285" y="1915341"/>
+          <a:ext cx="2607672" cy="2553788"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -4356,12 +4356,12 @@
         </a:fontRef>
       </dsp:style>
       <dsp:txBody>
-        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="53340" tIns="53340" rIns="53340" bIns="53340" numCol="1" spcCol="1270" anchor="t" anchorCtr="0">
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="114300" tIns="114300" rIns="114300" bIns="114300" numCol="1" spcCol="1270" anchor="t" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="l" defTabSz="622300">
+          <a:pPr marL="0" lvl="0" indent="0" algn="l" defTabSz="1333500">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -4374,12 +4374,12 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-IE" sz="1400" kern="1200"/>
+            <a:rPr lang="en-IE" sz="3000" kern="1200"/>
             <a:t>Spend Money</a:t>
           </a:r>
         </a:p>
         <a:p>
-          <a:pPr marL="57150" lvl="1" indent="-57150" algn="l" defTabSz="488950">
+          <a:pPr marL="228600" lvl="1" indent="-228600" algn="l" defTabSz="1022350">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -4392,12 +4392,12 @@
             <a:buChar char="•"/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-IE" sz="1100" kern="1200"/>
+            <a:rPr lang="en-IE" sz="2300" kern="1200"/>
             <a:t>Monthly Fixed Expenses</a:t>
           </a:r>
         </a:p>
         <a:p>
-          <a:pPr marL="57150" lvl="1" indent="-57150" algn="l" defTabSz="488950">
+          <a:pPr marL="228600" lvl="1" indent="-228600" algn="l" defTabSz="1022350">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -4410,14 +4410,14 @@
             <a:buChar char="•"/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-IE" sz="1100" kern="1200"/>
+            <a:rPr lang="en-IE" sz="2300" kern="1200"/>
             <a:t>Monthly Variable Expenses</a:t>
           </a:r>
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1653764" y="876525"/>
-        <a:ext cx="1264470" cy="990150"/>
+        <a:off x="3166951" y="2040007"/>
+        <a:ext cx="2358340" cy="2304456"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{F1BA3163-B742-47E9-9399-FD9E172DCCD4}">
@@ -4427,8 +4427,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3045469" y="822960"/>
-          <a:ext cx="1371600" cy="1097280"/>
+          <a:off x="5840312" y="1915341"/>
+          <a:ext cx="2607672" cy="2553788"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -4469,12 +4469,12 @@
         </a:fontRef>
       </dsp:style>
       <dsp:txBody>
-        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="53340" tIns="53340" rIns="53340" bIns="53340" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="114300" tIns="114300" rIns="114300" bIns="114300" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="622300">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="1333500">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -4487,14 +4487,14 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-IE" sz="1400" kern="1200"/>
+            <a:rPr lang="en-IE" sz="3000" kern="1200"/>
             <a:t>Track Money</a:t>
           </a:r>
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3099034" y="876525"/>
-        <a:ext cx="1264470" cy="990150"/>
+        <a:off x="5964978" y="2040007"/>
+        <a:ext cx="2358340" cy="2304456"/>
       </dsp:txXfrm>
     </dsp:sp>
   </dsp:spTree>
@@ -6719,15 +6719,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>278130</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>45720</xdr:rowOff>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>674370</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>160020</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>742950</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6754,16 +6754,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>331470</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>198120</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>556260</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>666750</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6795,7 +6795,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9289143" cy="6068786"/>
+    <xdr:ext cx="9289143" cy="6059714"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
@@ -7094,21 +7094,21 @@
   <sheetData>
     <row r="2" spans="2:17" ht="47.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="3"/>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
@@ -7163,362 +7163,362 @@
     </row>
     <row r="5" spans="2:17" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3"/>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="8">
         <v>725</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="8">
         <v>725</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="8">
         <v>725</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="8">
         <v>725</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="8">
         <v>725</v>
       </c>
-      <c r="I5" s="9">
+      <c r="I5" s="8">
         <v>725</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="8">
         <v>725</v>
       </c>
-      <c r="K5" s="9">
+      <c r="K5" s="8">
         <v>725</v>
       </c>
-      <c r="L5" s="9">
+      <c r="L5" s="8">
         <v>725</v>
       </c>
-      <c r="M5" s="9">
+      <c r="M5" s="8">
         <v>725</v>
       </c>
-      <c r="N5" s="9">
+      <c r="N5" s="8">
         <v>725</v>
       </c>
-      <c r="O5" s="9">
+      <c r="O5" s="8">
         <v>725</v>
       </c>
-      <c r="P5" s="8">
+      <c r="P5" s="7">
         <f t="shared" ref="P5:P11" si="0">SUM(D5:O5)</f>
         <v>8700</v>
       </c>
-      <c r="Q5" s="10">
+      <c r="Q5" s="9">
         <f t="shared" ref="Q5:Q10" si="1">P5/$P$11</f>
         <v>0.52858618385078071</v>
       </c>
     </row>
     <row r="6" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B6" s="3"/>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="10">
         <v>20</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="10">
         <v>20</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="10">
         <v>20</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="10">
         <v>20</v>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="10">
         <v>20</v>
       </c>
-      <c r="I6" s="11">
+      <c r="I6" s="10">
         <v>20</v>
       </c>
-      <c r="J6" s="11">
+      <c r="J6" s="10">
         <v>20</v>
       </c>
-      <c r="K6" s="11">
+      <c r="K6" s="10">
         <v>20</v>
       </c>
-      <c r="L6" s="11">
+      <c r="L6" s="10">
         <v>20</v>
       </c>
-      <c r="M6" s="11">
+      <c r="M6" s="10">
         <v>20</v>
       </c>
-      <c r="N6" s="11">
+      <c r="N6" s="10">
         <v>20</v>
       </c>
-      <c r="O6" s="11">
+      <c r="O6" s="10">
         <v>20</v>
       </c>
-      <c r="P6" s="8">
+      <c r="P6" s="7">
         <f t="shared" si="0"/>
         <v>240</v>
       </c>
-      <c r="Q6" s="10">
+      <c r="Q6" s="9">
         <f t="shared" si="1"/>
         <v>1.4581687830366365E-2</v>
       </c>
     </row>
     <row r="7" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B7" s="3"/>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="10">
         <v>400</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="10">
         <v>400</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="10">
         <v>400</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="10">
         <v>400</v>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="10">
         <v>10</v>
       </c>
-      <c r="I7" s="11">
+      <c r="I7" s="10">
         <v>5</v>
       </c>
-      <c r="J7" s="11">
+      <c r="J7" s="10">
         <v>17</v>
       </c>
-      <c r="K7" s="11">
+      <c r="K7" s="10">
         <v>8</v>
       </c>
-      <c r="L7" s="11">
+      <c r="L7" s="10">
         <v>10</v>
       </c>
-      <c r="M7" s="11">
+      <c r="M7" s="10">
         <v>15</v>
       </c>
-      <c r="N7" s="11">
+      <c r="N7" s="10">
         <v>25</v>
       </c>
-      <c r="O7" s="11">
+      <c r="O7" s="10">
         <v>35</v>
       </c>
-      <c r="P7" s="8">
+      <c r="P7" s="7">
         <f t="shared" si="0"/>
         <v>1725</v>
       </c>
-      <c r="Q7" s="10">
+      <c r="Q7" s="9">
         <f t="shared" si="1"/>
         <v>0.10480588128075825</v>
       </c>
     </row>
     <row r="8" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B8" s="3"/>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="10">
         <v>40</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="10">
         <v>40</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="10">
         <v>40</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="10">
         <v>40</v>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="10">
         <v>40</v>
       </c>
-      <c r="I8" s="11">
+      <c r="I8" s="10">
         <v>40</v>
       </c>
-      <c r="J8" s="11">
+      <c r="J8" s="10">
         <v>40</v>
       </c>
-      <c r="K8" s="11">
+      <c r="K8" s="10">
         <v>40</v>
       </c>
-      <c r="L8" s="11">
+      <c r="L8" s="10">
         <v>40</v>
       </c>
-      <c r="M8" s="11">
+      <c r="M8" s="10">
         <v>40</v>
       </c>
-      <c r="N8" s="11">
+      <c r="N8" s="10">
         <v>40</v>
       </c>
-      <c r="O8" s="11">
+      <c r="O8" s="10">
         <v>40</v>
       </c>
-      <c r="P8" s="8">
+      <c r="P8" s="7">
         <f t="shared" si="0"/>
         <v>480</v>
       </c>
-      <c r="Q8" s="10">
+      <c r="Q8" s="9">
         <f t="shared" si="1"/>
         <v>2.9163375660732731E-2</v>
       </c>
     </row>
     <row r="9" spans="2:17" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B9" s="3"/>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="10">
         <v>400</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="10">
         <v>450</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="10">
         <v>400</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="10">
         <v>400</v>
       </c>
-      <c r="H9" s="11">
+      <c r="H9" s="10">
         <v>450</v>
       </c>
-      <c r="I9" s="11">
+      <c r="I9" s="10">
         <v>400</v>
       </c>
-      <c r="J9" s="11">
+      <c r="J9" s="10">
         <v>450</v>
       </c>
-      <c r="K9" s="11">
+      <c r="K9" s="10">
         <v>350</v>
       </c>
-      <c r="L9" s="11">
+      <c r="L9" s="10">
         <v>400</v>
       </c>
-      <c r="M9" s="11">
+      <c r="M9" s="10">
         <v>450</v>
       </c>
-      <c r="N9" s="11">
+      <c r="N9" s="10">
         <v>350</v>
       </c>
-      <c r="O9" s="11">
+      <c r="O9" s="10">
         <v>450</v>
       </c>
-      <c r="P9" s="8">
+      <c r="P9" s="7">
         <f t="shared" si="0"/>
         <v>4950</v>
       </c>
-      <c r="Q9" s="10">
+      <c r="Q9" s="9">
         <f t="shared" si="1"/>
         <v>0.30074731150130629</v>
       </c>
     </row>
     <row r="10" spans="2:17" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="3"/>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="11">
         <v>15</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="11">
         <v>20</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="11">
         <v>15</v>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="11">
         <v>25</v>
       </c>
-      <c r="H10" s="12">
+      <c r="H10" s="11">
         <v>35</v>
       </c>
-      <c r="I10" s="12">
+      <c r="I10" s="11">
         <v>45</v>
       </c>
-      <c r="J10" s="12">
+      <c r="J10" s="11">
         <v>25</v>
       </c>
-      <c r="K10" s="12">
+      <c r="K10" s="11">
         <v>35</v>
       </c>
-      <c r="L10" s="12">
+      <c r="L10" s="11">
         <v>25</v>
       </c>
-      <c r="M10" s="12">
+      <c r="M10" s="11">
         <v>14</v>
       </c>
-      <c r="N10" s="12">
+      <c r="N10" s="11">
         <v>35</v>
       </c>
-      <c r="O10" s="12">
+      <c r="O10" s="11">
         <v>75</v>
       </c>
-      <c r="P10" s="8">
+      <c r="P10" s="7">
         <f t="shared" si="0"/>
         <v>364</v>
       </c>
-      <c r="Q10" s="10">
+      <c r="Q10" s="9">
         <f t="shared" si="1"/>
         <v>2.2115559876055655E-2</v>
       </c>
     </row>
     <row r="11" spans="2:17" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B11" s="3"/>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="12">
         <f t="shared" ref="D11:O11" si="2">SUM(D5:D10)</f>
         <v>1600</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="12">
         <f t="shared" si="2"/>
         <v>1655</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="12">
         <f t="shared" si="2"/>
         <v>1600</v>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="12">
         <f t="shared" si="2"/>
         <v>1610</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="12">
         <f t="shared" si="2"/>
         <v>1280</v>
       </c>
-      <c r="I11" s="13">
+      <c r="I11" s="12">
         <f t="shared" si="2"/>
         <v>1235</v>
       </c>
-      <c r="J11" s="13">
+      <c r="J11" s="12">
         <f t="shared" si="2"/>
         <v>1277</v>
       </c>
-      <c r="K11" s="13">
+      <c r="K11" s="12">
         <f t="shared" si="2"/>
         <v>1178</v>
       </c>
-      <c r="L11" s="13">
+      <c r="L11" s="12">
         <f t="shared" si="2"/>
         <v>1220</v>
       </c>
-      <c r="M11" s="13">
+      <c r="M11" s="12">
         <f t="shared" si="2"/>
         <v>1264</v>
       </c>
-      <c r="N11" s="13">
+      <c r="N11" s="12">
         <f t="shared" si="2"/>
         <v>1195</v>
       </c>
-      <c r="O11" s="13">
+      <c r="O11" s="12">
         <f t="shared" si="2"/>
         <v>1345</v>
       </c>
-      <c r="P11" s="8">
+      <c r="P11" s="7">
         <f t="shared" si="0"/>
         <v>16459</v>
       </c>
-      <c r="Q11" s="14">
+      <c r="Q11" s="13">
         <f>SUM(Q5:Q10)</f>
         <v>1</v>
       </c>
@@ -7531,51 +7531,51 @@
       <c r="C13" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="7">
         <f t="shared" ref="D13:O13" si="3">MIN(D5:D10)</f>
         <v>15</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="7">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F13" s="7">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="7">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="H13" s="8">
+      <c r="H13" s="7">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="I13" s="8">
+      <c r="I13" s="7">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="J13" s="8">
+      <c r="J13" s="7">
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
-      <c r="K13" s="8">
+      <c r="K13" s="7">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="L13" s="8">
+      <c r="L13" s="7">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="M13" s="8">
+      <c r="M13" s="7">
         <f t="shared" si="3"/>
         <v>14</v>
       </c>
-      <c r="N13" s="8">
+      <c r="N13" s="7">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="O13" s="8">
+      <c r="O13" s="7">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
@@ -7585,51 +7585,51 @@
       <c r="C14" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="7">
         <f t="shared" ref="D14:O14" si="4">MAX(D5:D10)</f>
         <v>725</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="7">
         <f t="shared" si="4"/>
         <v>725</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="7">
         <f t="shared" si="4"/>
         <v>725</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="7">
         <f t="shared" si="4"/>
         <v>725</v>
       </c>
-      <c r="H14" s="8">
+      <c r="H14" s="7">
         <f t="shared" si="4"/>
         <v>725</v>
       </c>
-      <c r="I14" s="8">
+      <c r="I14" s="7">
         <f t="shared" si="4"/>
         <v>725</v>
       </c>
-      <c r="J14" s="8">
+      <c r="J14" s="7">
         <f t="shared" si="4"/>
         <v>725</v>
       </c>
-      <c r="K14" s="8">
+      <c r="K14" s="7">
         <f t="shared" si="4"/>
         <v>725</v>
       </c>
-      <c r="L14" s="8">
+      <c r="L14" s="7">
         <f t="shared" si="4"/>
         <v>725</v>
       </c>
-      <c r="M14" s="8">
+      <c r="M14" s="7">
         <f t="shared" si="4"/>
         <v>725</v>
       </c>
-      <c r="N14" s="8">
+      <c r="N14" s="7">
         <f t="shared" si="4"/>
         <v>725</v>
       </c>
-      <c r="O14" s="8">
+      <c r="O14" s="7">
         <f t="shared" si="4"/>
         <v>725</v>
       </c>
@@ -7639,51 +7639,51 @@
       <c r="C15" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="7">
         <f t="shared" ref="D15:O15" si="5">AVERAGE(D5:D10)</f>
         <v>266.66666666666669</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="7">
         <f t="shared" si="5"/>
         <v>275.83333333333331</v>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="7">
         <f t="shared" si="5"/>
         <v>266.66666666666669</v>
       </c>
-      <c r="G15" s="8">
+      <c r="G15" s="7">
         <f t="shared" si="5"/>
         <v>268.33333333333331</v>
       </c>
-      <c r="H15" s="8">
+      <c r="H15" s="7">
         <f t="shared" si="5"/>
         <v>213.33333333333334</v>
       </c>
-      <c r="I15" s="8">
+      <c r="I15" s="7">
         <f t="shared" si="5"/>
         <v>205.83333333333334</v>
       </c>
-      <c r="J15" s="8">
+      <c r="J15" s="7">
         <f t="shared" si="5"/>
         <v>212.83333333333334</v>
       </c>
-      <c r="K15" s="8">
+      <c r="K15" s="7">
         <f t="shared" si="5"/>
         <v>196.33333333333334</v>
       </c>
-      <c r="L15" s="8">
+      <c r="L15" s="7">
         <f t="shared" si="5"/>
         <v>203.33333333333334</v>
       </c>
-      <c r="M15" s="8">
+      <c r="M15" s="7">
         <f t="shared" si="5"/>
         <v>210.66666666666666</v>
       </c>
-      <c r="N15" s="8">
+      <c r="N15" s="7">
         <f t="shared" si="5"/>
         <v>199.16666666666666</v>
       </c>
-      <c r="O15" s="8">
+      <c r="O15" s="7">
         <f t="shared" si="5"/>
         <v>224.16666666666666</v>
       </c>
@@ -7693,51 +7693,51 @@
       <c r="C16" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="7">
         <f t="shared" ref="D16:O16" si="6">COUNT(D5:D10)</f>
         <v>6</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="7">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="F16" s="8">
+      <c r="F16" s="7">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="G16" s="8">
+      <c r="G16" s="7">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="H16" s="8">
+      <c r="H16" s="7">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="I16" s="8">
+      <c r="I16" s="7">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="J16" s="8">
+      <c r="J16" s="7">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="K16" s="8">
+      <c r="K16" s="7">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="L16" s="8">
+      <c r="L16" s="7">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="M16" s="8">
+      <c r="M16" s="7">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="N16" s="8">
+      <c r="N16" s="7">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="O16" s="8">
+      <c r="O16" s="7">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
@@ -7746,7 +7746,7 @@
       <c r="D18" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="8">
         <v>100</v>
       </c>
     </row>
@@ -7754,7 +7754,7 @@
       <c r="D19" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="8">
         <v>150</v>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
       <c r="D20" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="8">
         <v>55</v>
       </c>
     </row>
@@ -7770,7 +7770,7 @@
       <c r="D21" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E21" s="9">
+      <c r="E21" s="8">
         <f>SUM(E18:E20)</f>
         <v>305</v>
       </c>
@@ -7779,7 +7779,7 @@
       <c r="D22" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E22" s="14">
+      <c r="E22" s="13">
         <v>0.08</v>
       </c>
     </row>
@@ -7787,7 +7787,7 @@
       <c r="D23" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E23" s="9">
+      <c r="E23" s="8">
         <f>E21*(E22+1)</f>
         <v>329.40000000000003</v>
       </c>
@@ -7801,8 +7801,12 @@
       <formula>250</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.70866141732283472" right="0.9055118110236221" top="0.74803149606299213" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;CMonthly Budget Test</oddHeader>
+    <oddFooter>&amp;R&amp;D&amp;T&amp;Z&amp;F&amp;F&amp;A&amp;P</oddFooter>
+  </headerFooter>
   <ignoredErrors>
     <ignoredError sqref="D11:O16" formulaRange="1"/>
   </ignoredErrors>

--- a/Udemy Excel 101.xlsx
+++ b/Udemy Excel 101.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="331" documentId="8_{8761CF19-0046-4715-B8FB-9230E793B6F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E9612EA-F344-47FB-8173-CB101B809232}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{9F602598-B120-46E6-997C-287E091787E5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9F602598-B120-46E6-997C-287E091787E5}"/>
   </bookViews>
   <sheets>
     <sheet name="Budget " sheetId="7" r:id="rId1"/>
@@ -4161,8 +4161,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="651918" y="0"/>
-          <a:ext cx="7388406" cy="6384471"/>
+          <a:off x="639508" y="0"/>
+          <a:ext cx="7247763" cy="6423660"/>
         </a:xfrm>
         <a:prstGeom prst="rightArrow">
           <a:avLst/>
@@ -4201,8 +4201,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="244257" y="1915341"/>
-          <a:ext cx="2607672" cy="2553788"/>
+          <a:off x="4521" y="1927098"/>
+          <a:ext cx="2717117" cy="2569464"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -4243,12 +4243,12 @@
         </a:fontRef>
       </dsp:style>
       <dsp:txBody>
-        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="114300" tIns="114300" rIns="114300" bIns="114300" numCol="1" spcCol="1270" anchor="t" anchorCtr="0">
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="118110" tIns="118110" rIns="118110" bIns="118110" numCol="1" spcCol="1270" anchor="t" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="l" defTabSz="1333500">
+          <a:pPr marL="0" lvl="0" indent="0" algn="l" defTabSz="1377950">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -4261,12 +4261,12 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-IE" sz="3000" kern="1200"/>
+            <a:rPr lang="en-IE" sz="3100" kern="1200"/>
             <a:t>Make Money</a:t>
           </a:r>
         </a:p>
         <a:p>
-          <a:pPr marL="228600" lvl="1" indent="-228600" algn="l" defTabSz="1022350">
+          <a:pPr marL="228600" lvl="1" indent="-228600" algn="l" defTabSz="1066800">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -4279,12 +4279,12 @@
             <a:buChar char="•"/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-IE" sz="2300" kern="1200"/>
+            <a:rPr lang="en-IE" sz="2400" kern="1200"/>
             <a:t> Work</a:t>
           </a:r>
         </a:p>
         <a:p>
-          <a:pPr marL="228600" lvl="1" indent="-228600" algn="l" defTabSz="1022350">
+          <a:pPr marL="228600" lvl="1" indent="-228600" algn="l" defTabSz="1066800">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -4297,14 +4297,14 @@
             <a:buChar char="•"/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-IE" sz="2300" kern="1200"/>
+            <a:rPr lang="en-IE" sz="2400" kern="1200"/>
             <a:t>Ask my Mom</a:t>
           </a:r>
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="368923" y="2040007"/>
-        <a:ext cx="2358340" cy="2304456"/>
+        <a:off x="129952" y="2052529"/>
+        <a:ext cx="2466255" cy="2318602"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{C75E2687-E3E1-4FB6-A473-6B5A0BA5A8EB}">
@@ -4314,8 +4314,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3042285" y="1915341"/>
-          <a:ext cx="2607672" cy="2553788"/>
+          <a:off x="2904831" y="1927098"/>
+          <a:ext cx="2717117" cy="2569464"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -4356,12 +4356,12 @@
         </a:fontRef>
       </dsp:style>
       <dsp:txBody>
-        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="114300" tIns="114300" rIns="114300" bIns="114300" numCol="1" spcCol="1270" anchor="t" anchorCtr="0">
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="118110" tIns="118110" rIns="118110" bIns="118110" numCol="1" spcCol="1270" anchor="t" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="l" defTabSz="1333500">
+          <a:pPr marL="0" lvl="0" indent="0" algn="l" defTabSz="1377950">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -4374,12 +4374,12 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-IE" sz="3000" kern="1200"/>
+            <a:rPr lang="en-IE" sz="3100" kern="1200"/>
             <a:t>Spend Money</a:t>
           </a:r>
         </a:p>
         <a:p>
-          <a:pPr marL="228600" lvl="1" indent="-228600" algn="l" defTabSz="1022350">
+          <a:pPr marL="228600" lvl="1" indent="-228600" algn="l" defTabSz="1066800">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -4392,12 +4392,12 @@
             <a:buChar char="•"/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-IE" sz="2300" kern="1200"/>
+            <a:rPr lang="en-IE" sz="2400" kern="1200"/>
             <a:t>Monthly Fixed Expenses</a:t>
           </a:r>
         </a:p>
         <a:p>
-          <a:pPr marL="228600" lvl="1" indent="-228600" algn="l" defTabSz="1022350">
+          <a:pPr marL="228600" lvl="1" indent="-228600" algn="l" defTabSz="1066800">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -4410,14 +4410,14 @@
             <a:buChar char="•"/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-IE" sz="2300" kern="1200"/>
+            <a:rPr lang="en-IE" sz="2400" kern="1200"/>
             <a:t>Monthly Variable Expenses</a:t>
           </a:r>
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3166951" y="2040007"/>
-        <a:ext cx="2358340" cy="2304456"/>
+        <a:off x="3030262" y="2052529"/>
+        <a:ext cx="2466255" cy="2318602"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{F1BA3163-B742-47E9-9399-FD9E172DCCD4}">
@@ -4427,8 +4427,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="5840312" y="1915341"/>
-          <a:ext cx="2607672" cy="2553788"/>
+          <a:off x="5805141" y="1927098"/>
+          <a:ext cx="2717117" cy="2569464"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -4469,12 +4469,12 @@
         </a:fontRef>
       </dsp:style>
       <dsp:txBody>
-        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="114300" tIns="114300" rIns="114300" bIns="114300" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="118110" tIns="118110" rIns="118110" bIns="118110" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="1333500">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="1377950">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -4487,14 +4487,14 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-IE" sz="3000" kern="1200"/>
+            <a:rPr lang="en-IE" sz="3100" kern="1200"/>
             <a:t>Track Money</a:t>
           </a:r>
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="5964978" y="2040007"/>
-        <a:ext cx="2358340" cy="2304456"/>
+        <a:off x="5930572" y="2052529"/>
+        <a:ext cx="2466255" cy="2318602"/>
       </dsp:txXfrm>
     </dsp:sp>
   </dsp:spTree>
